--- a/data/databases/a_facet.xlsx
+++ b/data/databases/a_facet.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yotto\YandexDisk-gasilin@inion.ru\Developments\e-Library_to_RETRO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yotto\CONVERTERS\INION\data\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE810C68-79B2-4D16-A183-A442FBE4F448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58924B2C-1208-45F8-9E3C-FFE21E3782DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="1200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2544" uniqueCount="1949">
   <si>
     <t>Аверроэс</t>
   </si>
@@ -3405,12 +3406,6 @@
     <t>XXI в.</t>
   </si>
   <si>
-    <t>ссср</t>
-  </si>
-  <si>
-    <t>СССР</t>
-  </si>
-  <si>
     <t>сша</t>
   </si>
   <si>
@@ -3441,96 +3436,12 @@
     <t>Франция</t>
   </si>
   <si>
-    <t>франции</t>
-  </si>
-  <si>
-    <t>Франции</t>
-  </si>
-  <si>
-    <t>францией</t>
-  </si>
-  <si>
-    <t>Францией</t>
-  </si>
-  <si>
-    <t>англия</t>
-  </si>
-  <si>
-    <t>Англия</t>
-  </si>
-  <si>
-    <t>англии</t>
-  </si>
-  <si>
-    <t>Англии</t>
-  </si>
-  <si>
-    <t>англией</t>
-  </si>
-  <si>
-    <t>Англией</t>
-  </si>
-  <si>
-    <t>китая</t>
-  </si>
-  <si>
-    <t>Китая</t>
-  </si>
-  <si>
-    <t>китаю</t>
-  </si>
-  <si>
-    <t>Китаю</t>
-  </si>
-  <si>
-    <t>китаем</t>
-  </si>
-  <si>
-    <t>Китаем</t>
-  </si>
-  <si>
-    <t>китае</t>
-  </si>
-  <si>
-    <t>Китае</t>
-  </si>
-  <si>
     <t>индия</t>
   </si>
   <si>
     <t>Индия</t>
   </si>
   <si>
-    <t>великобритан</t>
-  </si>
-  <si>
-    <t>Великобритан</t>
-  </si>
-  <si>
-    <t xml:space="preserve">китай </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Китай </t>
-  </si>
-  <si>
-    <t>индии</t>
-  </si>
-  <si>
-    <t>Индии</t>
-  </si>
-  <si>
-    <t>индией</t>
-  </si>
-  <si>
-    <t>Индией</t>
-  </si>
-  <si>
-    <t>герман</t>
-  </si>
-  <si>
-    <t>Герман</t>
-  </si>
-  <si>
     <t>италия</t>
   </si>
   <si>
@@ -3543,48 +3454,12 @@
     <t>Испания</t>
   </si>
   <si>
-    <t>италии</t>
-  </si>
-  <si>
-    <t>Италии</t>
-  </si>
-  <si>
-    <t>италией</t>
-  </si>
-  <si>
-    <t>Италией</t>
-  </si>
-  <si>
-    <t>испании</t>
-  </si>
-  <si>
-    <t>Испании</t>
-  </si>
-  <si>
-    <t>испанией</t>
-  </si>
-  <si>
-    <t>Испанией</t>
-  </si>
-  <si>
     <t>япония</t>
   </si>
   <si>
     <t>Япония</t>
   </si>
   <si>
-    <t>японии</t>
-  </si>
-  <si>
-    <t>японией</t>
-  </si>
-  <si>
-    <t>Японией</t>
-  </si>
-  <si>
-    <t>Японии</t>
-  </si>
-  <si>
     <t>мишель</t>
   </si>
   <si>
@@ -3631,13 +3506,2386 @@
   </si>
   <si>
     <t>Европой</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ai </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AI </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> eu </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EU </t>
+  </si>
+  <si>
+    <t>russia</t>
+  </si>
+  <si>
+    <t>Russia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> usa </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> USA </t>
+  </si>
+  <si>
+    <t>казахстан</t>
+  </si>
+  <si>
+    <t>Казахстан</t>
+  </si>
+  <si>
+    <t>армения</t>
+  </si>
+  <si>
+    <t>Армения</t>
+  </si>
+  <si>
+    <t>Абхазия</t>
+  </si>
+  <si>
+    <t>Австралия</t>
+  </si>
+  <si>
+    <t>Австрия</t>
+  </si>
+  <si>
+    <t>Азербайджан</t>
+  </si>
+  <si>
+    <t>Албания</t>
+  </si>
+  <si>
+    <t>Алжир</t>
+  </si>
+  <si>
+    <t>Ангола</t>
+  </si>
+  <si>
+    <t>Андорра</t>
+  </si>
+  <si>
+    <t>Антигуа и Барбуда</t>
+  </si>
+  <si>
+    <t>Аргентина</t>
+  </si>
+  <si>
+    <t>Афганистан</t>
+  </si>
+  <si>
+    <t>Багамские Острова</t>
+  </si>
+  <si>
+    <t>Бангладеш</t>
+  </si>
+  <si>
+    <t>Барбадос</t>
+  </si>
+  <si>
+    <t>Бахрейн</t>
+  </si>
+  <si>
+    <t>Белиз</t>
+  </si>
+  <si>
+    <t>Белоруссия</t>
+  </si>
+  <si>
+    <t>Бельгия</t>
+  </si>
+  <si>
+    <t>Бенин</t>
+  </si>
+  <si>
+    <t>Болгария</t>
+  </si>
+  <si>
+    <t>Боливия</t>
+  </si>
+  <si>
+    <t>Босния и Герцеговина</t>
+  </si>
+  <si>
+    <t>Ботсвана</t>
+  </si>
+  <si>
+    <t>Бразилия</t>
+  </si>
+  <si>
+    <t>Бруней</t>
+  </si>
+  <si>
+    <t>Буркина-Фасо</t>
+  </si>
+  <si>
+    <t>Бурунди</t>
+  </si>
+  <si>
+    <t>Бутан</t>
+  </si>
+  <si>
+    <t>Вануату</t>
+  </si>
+  <si>
+    <t>Ватикан</t>
+  </si>
+  <si>
+    <t>Великобритания</t>
+  </si>
+  <si>
+    <t>Венгрия</t>
+  </si>
+  <si>
+    <t>Венесуэла</t>
+  </si>
+  <si>
+    <t>Восточный Тимор</t>
+  </si>
+  <si>
+    <t>Вьетнам</t>
+  </si>
+  <si>
+    <t>Габон</t>
+  </si>
+  <si>
+    <t>Гаити</t>
+  </si>
+  <si>
+    <t>Гайана</t>
+  </si>
+  <si>
+    <t>Гамбия</t>
+  </si>
+  <si>
+    <t>Гана</t>
+  </si>
+  <si>
+    <t>Гватемала</t>
+  </si>
+  <si>
+    <t>Гвинея</t>
+  </si>
+  <si>
+    <t>Гвинея-Бисау</t>
+  </si>
+  <si>
+    <t>Германия</t>
+  </si>
+  <si>
+    <t>Гондурас</t>
+  </si>
+  <si>
+    <t>Гренада</t>
+  </si>
+  <si>
+    <t>Греция</t>
+  </si>
+  <si>
+    <t>Грузия</t>
+  </si>
+  <si>
+    <t>Дания</t>
+  </si>
+  <si>
+    <t>Джибути</t>
+  </si>
+  <si>
+    <t>Доминика</t>
+  </si>
+  <si>
+    <t>Доминиканская Республика</t>
+  </si>
+  <si>
+    <t>Европейский союз</t>
+  </si>
+  <si>
+    <t>Египет</t>
+  </si>
+  <si>
+    <t>Замбия</t>
+  </si>
+  <si>
+    <t>Зимбабве</t>
+  </si>
+  <si>
+    <t>Израиль</t>
+  </si>
+  <si>
+    <t>Индонезия</t>
+  </si>
+  <si>
+    <t>Иордания</t>
+  </si>
+  <si>
+    <t>Ирак</t>
+  </si>
+  <si>
+    <t>Иран</t>
+  </si>
+  <si>
+    <t>Ирландия</t>
+  </si>
+  <si>
+    <t>Исландия</t>
+  </si>
+  <si>
+    <t>Йемен</t>
+  </si>
+  <si>
+    <t>Кабо-Верде</t>
+  </si>
+  <si>
+    <t>Камбоджа</t>
+  </si>
+  <si>
+    <t>Камерун</t>
+  </si>
+  <si>
+    <t>Канада</t>
+  </si>
+  <si>
+    <t>Катар</t>
+  </si>
+  <si>
+    <t>Кения</t>
+  </si>
+  <si>
+    <t>Кипр</t>
+  </si>
+  <si>
+    <t>Киргизстан</t>
+  </si>
+  <si>
+    <t>Кирибати</t>
+  </si>
+  <si>
+    <t>Китай</t>
+  </si>
+  <si>
+    <t>Колумбия</t>
+  </si>
+  <si>
+    <t>Коморы</t>
+  </si>
+  <si>
+    <t>ДРК (Конго)</t>
+  </si>
+  <si>
+    <t>Республика Конго</t>
+  </si>
+  <si>
+    <t>КНДР</t>
+  </si>
+  <si>
+    <t>Республика Корея</t>
+  </si>
+  <si>
+    <t>Коста-Рика</t>
+  </si>
+  <si>
+    <t>Кот-д’Ивуар</t>
+  </si>
+  <si>
+    <t>Куба</t>
+  </si>
+  <si>
+    <t>Кувейт</t>
+  </si>
+  <si>
+    <t>Лаос</t>
+  </si>
+  <si>
+    <t>Латвия</t>
+  </si>
+  <si>
+    <t>Лесото</t>
+  </si>
+  <si>
+    <t>Либерия</t>
+  </si>
+  <si>
+    <t>Ливан</t>
+  </si>
+  <si>
+    <t>Ливия</t>
+  </si>
+  <si>
+    <t>Литва</t>
+  </si>
+  <si>
+    <t>Лихтенштейн</t>
+  </si>
+  <si>
+    <t>Люксембург</t>
+  </si>
+  <si>
+    <t>Маврикий</t>
+  </si>
+  <si>
+    <t>Мавритания</t>
+  </si>
+  <si>
+    <t>Мадагаскар</t>
+  </si>
+  <si>
+    <t>Северная Македония</t>
+  </si>
+  <si>
+    <t>Малави</t>
+  </si>
+  <si>
+    <t>Малайзия</t>
+  </si>
+  <si>
+    <t>Мали</t>
+  </si>
+  <si>
+    <t>Мальдивы</t>
+  </si>
+  <si>
+    <t>Мальта</t>
+  </si>
+  <si>
+    <t>Мальтийский орден</t>
+  </si>
+  <si>
+    <t>Марокко</t>
+  </si>
+  <si>
+    <t>Маршалловы Острова</t>
+  </si>
+  <si>
+    <t>Мексика</t>
+  </si>
+  <si>
+    <t>Мозамбик</t>
+  </si>
+  <si>
+    <t>Молдова</t>
+  </si>
+  <si>
+    <t>Монако</t>
+  </si>
+  <si>
+    <t>Монголия</t>
+  </si>
+  <si>
+    <t>Мьянма</t>
+  </si>
+  <si>
+    <t>Намибия</t>
+  </si>
+  <si>
+    <t>Науру</t>
+  </si>
+  <si>
+    <t>Непал</t>
+  </si>
+  <si>
+    <t>Нигер</t>
+  </si>
+  <si>
+    <t>Нигерия</t>
+  </si>
+  <si>
+    <t>Нидерланды</t>
+  </si>
+  <si>
+    <t>Никарагуа</t>
+  </si>
+  <si>
+    <t>Новая Зеландия</t>
+  </si>
+  <si>
+    <t>Норвегия</t>
+  </si>
+  <si>
+    <t>ОАЭ</t>
+  </si>
+  <si>
+    <t>Оман</t>
+  </si>
+  <si>
+    <t>Пакистан</t>
+  </si>
+  <si>
+    <t>Палау</t>
+  </si>
+  <si>
+    <t>Палестина</t>
+  </si>
+  <si>
+    <t>Панама</t>
+  </si>
+  <si>
+    <t>Папуа—Новая Гвинея</t>
+  </si>
+  <si>
+    <t>Парагвай</t>
+  </si>
+  <si>
+    <t>Перу</t>
+  </si>
+  <si>
+    <t>Польша</t>
+  </si>
+  <si>
+    <t>Португалия</t>
+  </si>
+  <si>
+    <t>Руанда</t>
+  </si>
+  <si>
+    <t>Румыния</t>
+  </si>
+  <si>
+    <t>Сальвадор</t>
+  </si>
+  <si>
+    <t>Самоа</t>
+  </si>
+  <si>
+    <t>Сан-Марино</t>
+  </si>
+  <si>
+    <t>Сан-Томеи Принсипи</t>
+  </si>
+  <si>
+    <t>Саудовская Аравия</t>
+  </si>
+  <si>
+    <t>Сейшельские Острова</t>
+  </si>
+  <si>
+    <t>Сенегал</t>
+  </si>
+  <si>
+    <t>Сент-Винсенти Гренадины</t>
+  </si>
+  <si>
+    <t>Сент-Китси Невис</t>
+  </si>
+  <si>
+    <t>Сент-Люсия</t>
+  </si>
+  <si>
+    <t>Сербия</t>
+  </si>
+  <si>
+    <t>Сингапур</t>
+  </si>
+  <si>
+    <t>Сирия</t>
+  </si>
+  <si>
+    <t>Словакия</t>
+  </si>
+  <si>
+    <t>Словения</t>
+  </si>
+  <si>
+    <t>Соломоновы острова</t>
+  </si>
+  <si>
+    <t>Сомали</t>
+  </si>
+  <si>
+    <t>Судан</t>
+  </si>
+  <si>
+    <t>Суринам</t>
+  </si>
+  <si>
+    <t>Сьерра-Леоне</t>
+  </si>
+  <si>
+    <t>Таджикистан</t>
+  </si>
+  <si>
+    <t>Таиланд</t>
+  </si>
+  <si>
+    <t>Танзания</t>
+  </si>
+  <si>
+    <t>Того</t>
+  </si>
+  <si>
+    <t>Тонга</t>
+  </si>
+  <si>
+    <t>Тринидад и Тобаго</t>
+  </si>
+  <si>
+    <t>Тувалу</t>
+  </si>
+  <si>
+    <t>Тунис</t>
+  </si>
+  <si>
+    <t>Туркменистан</t>
+  </si>
+  <si>
+    <t>Турция</t>
+  </si>
+  <si>
+    <t>Уганда</t>
+  </si>
+  <si>
+    <t>Узбекистан</t>
+  </si>
+  <si>
+    <t>Украина</t>
+  </si>
+  <si>
+    <t>Уругвай</t>
+  </si>
+  <si>
+    <t>Федеративные Штаты Микронезии</t>
+  </si>
+  <si>
+    <t>Фиджи</t>
+  </si>
+  <si>
+    <t>Филиппины</t>
+  </si>
+  <si>
+    <t>Финляндия</t>
+  </si>
+  <si>
+    <t>Хорватия</t>
+  </si>
+  <si>
+    <t>ЦАР</t>
+  </si>
+  <si>
+    <t>Чад</t>
+  </si>
+  <si>
+    <t>Черногория</t>
+  </si>
+  <si>
+    <t>Чехия</t>
+  </si>
+  <si>
+    <t>Чили</t>
+  </si>
+  <si>
+    <t>Швейцария</t>
+  </si>
+  <si>
+    <t>Швеция</t>
+  </si>
+  <si>
+    <t>Шри-Ланка</t>
+  </si>
+  <si>
+    <t>Эквадор</t>
+  </si>
+  <si>
+    <t>Экваториальная Гвинея</t>
+  </si>
+  <si>
+    <t>Эритрея</t>
+  </si>
+  <si>
+    <t>Эсватини</t>
+  </si>
+  <si>
+    <t>Эстония</t>
+  </si>
+  <si>
+    <t>Эфиопия</t>
+  </si>
+  <si>
+    <t>ЮАР</t>
+  </si>
+  <si>
+    <t>Южная Осетия</t>
+  </si>
+  <si>
+    <t>Южный Судан</t>
+  </si>
+  <si>
+    <t>Ямайка</t>
+  </si>
+  <si>
+    <t>Abkhazia</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>Azerbaijan</t>
+  </si>
+  <si>
+    <t>Albania</t>
+  </si>
+  <si>
+    <t>Algeria</t>
+  </si>
+  <si>
+    <t>Angola</t>
+  </si>
+  <si>
+    <t>Andorra</t>
+  </si>
+  <si>
+    <t>Antigua and Barbuda</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Armenia</t>
+  </si>
+  <si>
+    <t>Afghanistan</t>
+  </si>
+  <si>
+    <t>Bahamas</t>
+  </si>
+  <si>
+    <t>Bangladesh</t>
+  </si>
+  <si>
+    <t>Barbados</t>
+  </si>
+  <si>
+    <t>Bahrain</t>
+  </si>
+  <si>
+    <t>Belize</t>
+  </si>
+  <si>
+    <t>Belarus</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Benin</t>
+  </si>
+  <si>
+    <t>Bulgaria</t>
+  </si>
+  <si>
+    <t>Bolivia</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina</t>
+  </si>
+  <si>
+    <t>Botswana</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Brunei</t>
+  </si>
+  <si>
+    <t>Burkina Faso</t>
+  </si>
+  <si>
+    <t>Burundi</t>
+  </si>
+  <si>
+    <t>Bhutan</t>
+  </si>
+  <si>
+    <t>Vanuatu</t>
+  </si>
+  <si>
+    <t>Vatican City</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>Venezuela</t>
+  </si>
+  <si>
+    <t>East Timor</t>
+  </si>
+  <si>
+    <t>Vietnam</t>
+  </si>
+  <si>
+    <t>Gabon</t>
+  </si>
+  <si>
+    <t>Haiti</t>
+  </si>
+  <si>
+    <t>Guyana</t>
+  </si>
+  <si>
+    <t>Gambia</t>
+  </si>
+  <si>
+    <t>Ghana</t>
+  </si>
+  <si>
+    <t>Guatemala</t>
+  </si>
+  <si>
+    <t>Guinea</t>
+  </si>
+  <si>
+    <t>Guinea-Bissau</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Honduras</t>
+  </si>
+  <si>
+    <t>Grenada</t>
+  </si>
+  <si>
+    <t>Greece</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Djibouti</t>
+  </si>
+  <si>
+    <t>Dominica</t>
+  </si>
+  <si>
+    <t>Dominican Republic</t>
+  </si>
+  <si>
+    <t>European Union</t>
+  </si>
+  <si>
+    <t>Egypt</t>
+  </si>
+  <si>
+    <t>Zambia</t>
+  </si>
+  <si>
+    <t>Zimbabwe</t>
+  </si>
+  <si>
+    <t>Israel</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>Jordan</t>
+  </si>
+  <si>
+    <t>Iraq</t>
+  </si>
+  <si>
+    <t>Iran</t>
+  </si>
+  <si>
+    <t>Ireland</t>
+  </si>
+  <si>
+    <t>Iceland</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Yemen</t>
+  </si>
+  <si>
+    <t>Cape Verde</t>
+  </si>
+  <si>
+    <t>Kazakhstan</t>
+  </si>
+  <si>
+    <t>Cambodia</t>
+  </si>
+  <si>
+    <t>Cameroon</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Qatar</t>
+  </si>
+  <si>
+    <t>Kenya</t>
+  </si>
+  <si>
+    <t>Cyprus</t>
+  </si>
+  <si>
+    <t>Kyrgyzstan</t>
+  </si>
+  <si>
+    <t>Kiribati</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Comoros</t>
+  </si>
+  <si>
+    <t>DRC (Congo)</t>
+  </si>
+  <si>
+    <t>Republic of the Congo</t>
+  </si>
+  <si>
+    <t>Republic of Korea</t>
+  </si>
+  <si>
+    <t>Costa Rica</t>
+  </si>
+  <si>
+    <t>Côte d'Ivoire</t>
+  </si>
+  <si>
+    <t>Kuwait</t>
+  </si>
+  <si>
+    <t>Latvia</t>
+  </si>
+  <si>
+    <t>Lesotho</t>
+  </si>
+  <si>
+    <t>Liberia</t>
+  </si>
+  <si>
+    <t>Lebanon</t>
+  </si>
+  <si>
+    <t>Libya</t>
+  </si>
+  <si>
+    <t>Lithuania</t>
+  </si>
+  <si>
+    <t>Liechtenstein</t>
+  </si>
+  <si>
+    <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>Mauritius</t>
+  </si>
+  <si>
+    <t>Mauritania</t>
+  </si>
+  <si>
+    <t>Madagascar</t>
+  </si>
+  <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
+    <t>Malawi</t>
+  </si>
+  <si>
+    <t>Malaysia</t>
+  </si>
+  <si>
+    <t>Maldives</t>
+  </si>
+  <si>
+    <t>Malta</t>
+  </si>
+  <si>
+    <t>Order of Malta</t>
+  </si>
+  <si>
+    <t>Morocco</t>
+  </si>
+  <si>
+    <t>Marshall Islands</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>Mozambique</t>
+  </si>
+  <si>
+    <t>Moldova</t>
+  </si>
+  <si>
+    <t>Principality of Monaco</t>
+  </si>
+  <si>
+    <t>Mongolia</t>
+  </si>
+  <si>
+    <t>Myanmar</t>
+  </si>
+  <si>
+    <t>Namibia</t>
+  </si>
+  <si>
+    <t>Nauru</t>
+  </si>
+  <si>
+    <t>Nepal</t>
+  </si>
+  <si>
+    <t>Niger</t>
+  </si>
+  <si>
+    <t>Nigeria</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Nicaragua</t>
+  </si>
+  <si>
+    <t>New Zealand</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Oman</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>Palau</t>
+  </si>
+  <si>
+    <t>Palestine</t>
+  </si>
+  <si>
+    <t>Panama</t>
+  </si>
+  <si>
+    <t>Папуа-Новая Гвинея</t>
+  </si>
+  <si>
+    <t>Papua New Guinea</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>Rwanda</t>
+  </si>
+  <si>
+    <t>Romania</t>
+  </si>
+  <si>
+    <t>El Salvador</t>
+  </si>
+  <si>
+    <t>Samoa</t>
+  </si>
+  <si>
+    <t>San Marino</t>
+  </si>
+  <si>
+    <t>São Tomé Príncipe</t>
+  </si>
+  <si>
+    <t>Saudi Arabia</t>
+  </si>
+  <si>
+    <t>Seychelles</t>
+  </si>
+  <si>
+    <t>Senegal</t>
+  </si>
+  <si>
+    <t>Saint Vincent of the Grenadines</t>
+  </si>
+  <si>
+    <t>Saint Kittsey Nevis</t>
+  </si>
+  <si>
+    <t>Saint Lucia</t>
+  </si>
+  <si>
+    <t>Serbia</t>
+  </si>
+  <si>
+    <t>Singapore</t>
+  </si>
+  <si>
+    <t>Syria</t>
+  </si>
+  <si>
+    <t>Slovakia</t>
+  </si>
+  <si>
+    <t>Slovenia</t>
+  </si>
+  <si>
+    <t>Solomon Islands</t>
+  </si>
+  <si>
+    <t>Somalia</t>
+  </si>
+  <si>
+    <t>Sudan</t>
+  </si>
+  <si>
+    <t>Suriname</t>
+  </si>
+  <si>
+    <t>Sierra Leone</t>
+  </si>
+  <si>
+    <t>Thailand</t>
+  </si>
+  <si>
+    <t>Tanzania</t>
+  </si>
+  <si>
+    <t>Togo</t>
+  </si>
+  <si>
+    <t>Tonga</t>
+  </si>
+  <si>
+    <t>Trinidad and Tobago</t>
+  </si>
+  <si>
+    <t>Tuvalu</t>
+  </si>
+  <si>
+    <t>Tunisia</t>
+  </si>
+  <si>
+    <t>Turkmenistan</t>
+  </si>
+  <si>
+    <t>Turkey</t>
+  </si>
+  <si>
+    <t>Uganda</t>
+  </si>
+  <si>
+    <t>Uzbekistan</t>
+  </si>
+  <si>
+    <t>Ukraine</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
+  </si>
+  <si>
+    <t>Federated States of Micronesia</t>
+  </si>
+  <si>
+    <t>Philippines</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Croatia</t>
+  </si>
+  <si>
+    <t>Chad</t>
+  </si>
+  <si>
+    <t>Montenegro</t>
+  </si>
+  <si>
+    <t>Czech Republic</t>
+  </si>
+  <si>
+    <t>Chile</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Sri Lanka</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Equatorial Guinea</t>
+  </si>
+  <si>
+    <t>Eritrea</t>
+  </si>
+  <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
+    <t>Estonia</t>
+  </si>
+  <si>
+    <t>Ethiopia</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
+    <t>South Ossetia</t>
+  </si>
+  <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
+    <t>Jamaica</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fiji </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Peru </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> UAE </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mali </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Laos </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cuba </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DPRK </t>
+  </si>
+  <si>
+    <t>абхазия</t>
+  </si>
+  <si>
+    <t>австралия</t>
+  </si>
+  <si>
+    <t>австрия</t>
+  </si>
+  <si>
+    <t>азербайджан</t>
+  </si>
+  <si>
+    <t>албания</t>
+  </si>
+  <si>
+    <t>алжир</t>
+  </si>
+  <si>
+    <t>ангола</t>
+  </si>
+  <si>
+    <t>андорра</t>
+  </si>
+  <si>
+    <t>антигуа и барбуда</t>
+  </si>
+  <si>
+    <t>аргентина</t>
+  </si>
+  <si>
+    <t>афганистан</t>
+  </si>
+  <si>
+    <t>багамские острова</t>
+  </si>
+  <si>
+    <t>бангладеш</t>
+  </si>
+  <si>
+    <t>барбадос</t>
+  </si>
+  <si>
+    <t>бахрейн</t>
+  </si>
+  <si>
+    <t>белиз</t>
+  </si>
+  <si>
+    <t>белоруссия</t>
+  </si>
+  <si>
+    <t>бельгия</t>
+  </si>
+  <si>
+    <t>бенин</t>
+  </si>
+  <si>
+    <t>болгария</t>
+  </si>
+  <si>
+    <t>боливия</t>
+  </si>
+  <si>
+    <t>босния и герцеговина</t>
+  </si>
+  <si>
+    <t>ботсвана</t>
+  </si>
+  <si>
+    <t>бразилия</t>
+  </si>
+  <si>
+    <t>бруней</t>
+  </si>
+  <si>
+    <t>буркина-фасо</t>
+  </si>
+  <si>
+    <t>бурунди</t>
+  </si>
+  <si>
+    <t>бутан</t>
+  </si>
+  <si>
+    <t>вануату</t>
+  </si>
+  <si>
+    <t>ватикан</t>
+  </si>
+  <si>
+    <t>великобритания</t>
+  </si>
+  <si>
+    <t>венгрия</t>
+  </si>
+  <si>
+    <t>венесуэла</t>
+  </si>
+  <si>
+    <t>восточный тимор</t>
+  </si>
+  <si>
+    <t>вьетнам</t>
+  </si>
+  <si>
+    <t>габон</t>
+  </si>
+  <si>
+    <t>гаити</t>
+  </si>
+  <si>
+    <t>гайана</t>
+  </si>
+  <si>
+    <t>гамбия</t>
+  </si>
+  <si>
+    <t>гана</t>
+  </si>
+  <si>
+    <t>гватемала</t>
+  </si>
+  <si>
+    <t>гвинея</t>
+  </si>
+  <si>
+    <t>гвинея-бисау</t>
+  </si>
+  <si>
+    <t>германия</t>
+  </si>
+  <si>
+    <t>гондурас</t>
+  </si>
+  <si>
+    <t>гренада</t>
+  </si>
+  <si>
+    <t>греция</t>
+  </si>
+  <si>
+    <t>грузия</t>
+  </si>
+  <si>
+    <t>дания</t>
+  </si>
+  <si>
+    <t>джибути</t>
+  </si>
+  <si>
+    <t>доминика</t>
+  </si>
+  <si>
+    <t>доминиканская республика</t>
+  </si>
+  <si>
+    <t>европейский союз</t>
+  </si>
+  <si>
+    <t>египет</t>
+  </si>
+  <si>
+    <t>замбия</t>
+  </si>
+  <si>
+    <t>зимбабве</t>
+  </si>
+  <si>
+    <t>израиль</t>
+  </si>
+  <si>
+    <t>индонезия</t>
+  </si>
+  <si>
+    <t>иордания</t>
+  </si>
+  <si>
+    <t>ирак</t>
+  </si>
+  <si>
+    <t>иран</t>
+  </si>
+  <si>
+    <t>ирландия</t>
+  </si>
+  <si>
+    <t>исландия</t>
+  </si>
+  <si>
+    <t>йемен</t>
+  </si>
+  <si>
+    <t>кабо-верде</t>
+  </si>
+  <si>
+    <t>камбоджа</t>
+  </si>
+  <si>
+    <t>камерун</t>
+  </si>
+  <si>
+    <t>канада</t>
+  </si>
+  <si>
+    <t>катар</t>
+  </si>
+  <si>
+    <t>кения</t>
+  </si>
+  <si>
+    <t>кипр</t>
+  </si>
+  <si>
+    <t>киргизстан</t>
+  </si>
+  <si>
+    <t>кирибати</t>
+  </si>
+  <si>
+    <t>китай</t>
+  </si>
+  <si>
+    <t>колумбия</t>
+  </si>
+  <si>
+    <t>коморы</t>
+  </si>
+  <si>
+    <t>дрк (конго)</t>
+  </si>
+  <si>
+    <t>республика конго</t>
+  </si>
+  <si>
+    <t>кндр</t>
+  </si>
+  <si>
+    <t>республика корея</t>
+  </si>
+  <si>
+    <t>коста-рика</t>
+  </si>
+  <si>
+    <t>кот-д’ивуар</t>
+  </si>
+  <si>
+    <t>куба</t>
+  </si>
+  <si>
+    <t>кувейт</t>
+  </si>
+  <si>
+    <t>лаос</t>
+  </si>
+  <si>
+    <t>латвия</t>
+  </si>
+  <si>
+    <t>лесото</t>
+  </si>
+  <si>
+    <t>либерия</t>
+  </si>
+  <si>
+    <t>ливан</t>
+  </si>
+  <si>
+    <t>ливия</t>
+  </si>
+  <si>
+    <t>литва</t>
+  </si>
+  <si>
+    <t>лихтенштейн</t>
+  </si>
+  <si>
+    <t>люксембург</t>
+  </si>
+  <si>
+    <t>маврикий</t>
+  </si>
+  <si>
+    <t>мавритания</t>
+  </si>
+  <si>
+    <t>мадагаскар</t>
+  </si>
+  <si>
+    <t>северная македония</t>
+  </si>
+  <si>
+    <t>малави</t>
+  </si>
+  <si>
+    <t>малайзия</t>
+  </si>
+  <si>
+    <t>мали</t>
+  </si>
+  <si>
+    <t>мальдивы</t>
+  </si>
+  <si>
+    <t>мальта</t>
+  </si>
+  <si>
+    <t>мальтийский орден</t>
+  </si>
+  <si>
+    <t>марокко</t>
+  </si>
+  <si>
+    <t>маршалловы острова</t>
+  </si>
+  <si>
+    <t>мексика</t>
+  </si>
+  <si>
+    <t>мозамбик</t>
+  </si>
+  <si>
+    <t>молдова</t>
+  </si>
+  <si>
+    <t>монако</t>
+  </si>
+  <si>
+    <t>монголия</t>
+  </si>
+  <si>
+    <t>мьянма</t>
+  </si>
+  <si>
+    <t>намибия</t>
+  </si>
+  <si>
+    <t>науру</t>
+  </si>
+  <si>
+    <t>непал</t>
+  </si>
+  <si>
+    <t>нигер</t>
+  </si>
+  <si>
+    <t>нигерия</t>
+  </si>
+  <si>
+    <t>нидерланды</t>
+  </si>
+  <si>
+    <t>никарагуа</t>
+  </si>
+  <si>
+    <t>новая зеландия</t>
+  </si>
+  <si>
+    <t>норвегия</t>
+  </si>
+  <si>
+    <t>оаэ</t>
+  </si>
+  <si>
+    <t>оман</t>
+  </si>
+  <si>
+    <t>пакистан</t>
+  </si>
+  <si>
+    <t>палау</t>
+  </si>
+  <si>
+    <t>палестина</t>
+  </si>
+  <si>
+    <t>панама</t>
+  </si>
+  <si>
+    <t>папуа—новая гвинея</t>
+  </si>
+  <si>
+    <t>парагвай</t>
+  </si>
+  <si>
+    <t>перу</t>
+  </si>
+  <si>
+    <t>польша</t>
+  </si>
+  <si>
+    <t>португалия</t>
+  </si>
+  <si>
+    <t>руанда</t>
+  </si>
+  <si>
+    <t>румыния</t>
+  </si>
+  <si>
+    <t>сальвадор</t>
+  </si>
+  <si>
+    <t>самоа</t>
+  </si>
+  <si>
+    <t>сан-марино</t>
+  </si>
+  <si>
+    <t>сан-томеи принсипи</t>
+  </si>
+  <si>
+    <t>саудовская аравия</t>
+  </si>
+  <si>
+    <t>сейшельские острова</t>
+  </si>
+  <si>
+    <t>сенегал</t>
+  </si>
+  <si>
+    <t>сент-винсенти гренадины</t>
+  </si>
+  <si>
+    <t>сент-китси невис</t>
+  </si>
+  <si>
+    <t>сент-люсия</t>
+  </si>
+  <si>
+    <t>сербия</t>
+  </si>
+  <si>
+    <t>сингапур</t>
+  </si>
+  <si>
+    <t>сирия</t>
+  </si>
+  <si>
+    <t>словакия</t>
+  </si>
+  <si>
+    <t>словения</t>
+  </si>
+  <si>
+    <t>соломоновы острова</t>
+  </si>
+  <si>
+    <t>сомали</t>
+  </si>
+  <si>
+    <t>судан</t>
+  </si>
+  <si>
+    <t>суринам</t>
+  </si>
+  <si>
+    <t>сьерра-леоне</t>
+  </si>
+  <si>
+    <t>таджикистан</t>
+  </si>
+  <si>
+    <t>таиланд</t>
+  </si>
+  <si>
+    <t>танзания</t>
+  </si>
+  <si>
+    <t>того</t>
+  </si>
+  <si>
+    <t>тонга</t>
+  </si>
+  <si>
+    <t>тринидад и тобаго</t>
+  </si>
+  <si>
+    <t>тувалу</t>
+  </si>
+  <si>
+    <t>тунис</t>
+  </si>
+  <si>
+    <t>туркменистан</t>
+  </si>
+  <si>
+    <t>турция</t>
+  </si>
+  <si>
+    <t>уганда</t>
+  </si>
+  <si>
+    <t>узбекистан</t>
+  </si>
+  <si>
+    <t>украина</t>
+  </si>
+  <si>
+    <t>уругвай</t>
+  </si>
+  <si>
+    <t>федеративные штаты микронезии</t>
+  </si>
+  <si>
+    <t>фиджи</t>
+  </si>
+  <si>
+    <t>филиппины</t>
+  </si>
+  <si>
+    <t>финляндия</t>
+  </si>
+  <si>
+    <t>хорватия</t>
+  </si>
+  <si>
+    <t>цар</t>
+  </si>
+  <si>
+    <t>чад</t>
+  </si>
+  <si>
+    <t>черногория</t>
+  </si>
+  <si>
+    <t>чехия</t>
+  </si>
+  <si>
+    <t>чили</t>
+  </si>
+  <si>
+    <t>швейцария</t>
+  </si>
+  <si>
+    <t>швеция</t>
+  </si>
+  <si>
+    <t>шри-ланка</t>
+  </si>
+  <si>
+    <t>эквадор</t>
+  </si>
+  <si>
+    <t>экваториальная гвинея</t>
+  </si>
+  <si>
+    <t>эритрея</t>
+  </si>
+  <si>
+    <t>эсватини</t>
+  </si>
+  <si>
+    <t>эстония</t>
+  </si>
+  <si>
+    <t>эфиопия</t>
+  </si>
+  <si>
+    <t>юар</t>
+  </si>
+  <si>
+    <t>южная осетия</t>
+  </si>
+  <si>
+    <t>южный судан</t>
+  </si>
+  <si>
+    <t>ямайка</t>
+  </si>
+  <si>
+    <t>abkhazia</t>
+  </si>
+  <si>
+    <t>australia</t>
+  </si>
+  <si>
+    <t>austria</t>
+  </si>
+  <si>
+    <t>azerbaijan</t>
+  </si>
+  <si>
+    <t>albania</t>
+  </si>
+  <si>
+    <t>algeria</t>
+  </si>
+  <si>
+    <t>angola</t>
+  </si>
+  <si>
+    <t>andorra</t>
+  </si>
+  <si>
+    <t>antigua and barbuda</t>
+  </si>
+  <si>
+    <t>argentina</t>
+  </si>
+  <si>
+    <t>armenia</t>
+  </si>
+  <si>
+    <t>afghanistan</t>
+  </si>
+  <si>
+    <t>bahamas</t>
+  </si>
+  <si>
+    <t>bangladesh</t>
+  </si>
+  <si>
+    <t>barbados</t>
+  </si>
+  <si>
+    <t>bahrain</t>
+  </si>
+  <si>
+    <t>belize</t>
+  </si>
+  <si>
+    <t>belarus</t>
+  </si>
+  <si>
+    <t>belgium</t>
+  </si>
+  <si>
+    <t>benin</t>
+  </si>
+  <si>
+    <t>bulgaria</t>
+  </si>
+  <si>
+    <t>bolivia</t>
+  </si>
+  <si>
+    <t>bosnia and herzegovina</t>
+  </si>
+  <si>
+    <t>botswana</t>
+  </si>
+  <si>
+    <t>brazil</t>
+  </si>
+  <si>
+    <t>brunei</t>
+  </si>
+  <si>
+    <t>burkina faso</t>
+  </si>
+  <si>
+    <t>burundi</t>
+  </si>
+  <si>
+    <t>bhutan</t>
+  </si>
+  <si>
+    <t>vanuatu</t>
+  </si>
+  <si>
+    <t>vatican city</t>
+  </si>
+  <si>
+    <t>united kingdom</t>
+  </si>
+  <si>
+    <t>hungary</t>
+  </si>
+  <si>
+    <t>venezuela</t>
+  </si>
+  <si>
+    <t>east timor</t>
+  </si>
+  <si>
+    <t>vietnam</t>
+  </si>
+  <si>
+    <t>gabon</t>
+  </si>
+  <si>
+    <t>haiti</t>
+  </si>
+  <si>
+    <t>guyana</t>
+  </si>
+  <si>
+    <t>gambia</t>
+  </si>
+  <si>
+    <t>ghana</t>
+  </si>
+  <si>
+    <t>guatemala</t>
+  </si>
+  <si>
+    <t>guinea</t>
+  </si>
+  <si>
+    <t>guinea-bissau</t>
+  </si>
+  <si>
+    <t>germany</t>
+  </si>
+  <si>
+    <t>honduras</t>
+  </si>
+  <si>
+    <t>grenada</t>
+  </si>
+  <si>
+    <t>greece</t>
+  </si>
+  <si>
+    <t>georgia</t>
+  </si>
+  <si>
+    <t>denmark</t>
+  </si>
+  <si>
+    <t>djibouti</t>
+  </si>
+  <si>
+    <t>dominica</t>
+  </si>
+  <si>
+    <t>dominican republic</t>
+  </si>
+  <si>
+    <t>european union</t>
+  </si>
+  <si>
+    <t>egypt</t>
+  </si>
+  <si>
+    <t>zambia</t>
+  </si>
+  <si>
+    <t>zimbabwe</t>
+  </si>
+  <si>
+    <t>israel</t>
+  </si>
+  <si>
+    <t>india</t>
+  </si>
+  <si>
+    <t>indonesia</t>
+  </si>
+  <si>
+    <t>jordan</t>
+  </si>
+  <si>
+    <t>iraq</t>
+  </si>
+  <si>
+    <t>iran</t>
+  </si>
+  <si>
+    <t>ireland</t>
+  </si>
+  <si>
+    <t>iceland</t>
+  </si>
+  <si>
+    <t>spain</t>
+  </si>
+  <si>
+    <t>italy</t>
+  </si>
+  <si>
+    <t>yemen</t>
+  </si>
+  <si>
+    <t>cape verde</t>
+  </si>
+  <si>
+    <t>kazakhstan</t>
+  </si>
+  <si>
+    <t>cambodia</t>
+  </si>
+  <si>
+    <t>cameroon</t>
+  </si>
+  <si>
+    <t>canada</t>
+  </si>
+  <si>
+    <t>qatar</t>
+  </si>
+  <si>
+    <t>kenya</t>
+  </si>
+  <si>
+    <t>cyprus</t>
+  </si>
+  <si>
+    <t>kyrgyzstan</t>
+  </si>
+  <si>
+    <t>kiribati</t>
+  </si>
+  <si>
+    <t>china</t>
+  </si>
+  <si>
+    <t>colombia</t>
+  </si>
+  <si>
+    <t>comoros</t>
+  </si>
+  <si>
+    <t>drc (congo)</t>
+  </si>
+  <si>
+    <t>republic of the congo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> dprk </t>
+  </si>
+  <si>
+    <t>republic of korea</t>
+  </si>
+  <si>
+    <t>costa rica</t>
+  </si>
+  <si>
+    <t>côte d'ivoire</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cuba </t>
+  </si>
+  <si>
+    <t>kuwait</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> laos </t>
+  </si>
+  <si>
+    <t>latvia</t>
+  </si>
+  <si>
+    <t>lesotho</t>
+  </si>
+  <si>
+    <t>liberia</t>
+  </si>
+  <si>
+    <t>lebanon</t>
+  </si>
+  <si>
+    <t>libya</t>
+  </si>
+  <si>
+    <t>lithuania</t>
+  </si>
+  <si>
+    <t>liechtenstein</t>
+  </si>
+  <si>
+    <t>luxembourg</t>
+  </si>
+  <si>
+    <t>mauritius</t>
+  </si>
+  <si>
+    <t>mauritania</t>
+  </si>
+  <si>
+    <t>madagascar</t>
+  </si>
+  <si>
+    <t>north macedonia</t>
+  </si>
+  <si>
+    <t>malawi</t>
+  </si>
+  <si>
+    <t>malaysia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> mali </t>
+  </si>
+  <si>
+    <t>maldives</t>
+  </si>
+  <si>
+    <t>malta</t>
+  </si>
+  <si>
+    <t>order of malta</t>
+  </si>
+  <si>
+    <t>morocco</t>
+  </si>
+  <si>
+    <t>marshall islands</t>
+  </si>
+  <si>
+    <t>mexico</t>
+  </si>
+  <si>
+    <t>mozambique</t>
+  </si>
+  <si>
+    <t>moldova</t>
+  </si>
+  <si>
+    <t>principality of monaco</t>
+  </si>
+  <si>
+    <t>mongolia</t>
+  </si>
+  <si>
+    <t>myanmar</t>
+  </si>
+  <si>
+    <t>namibia</t>
+  </si>
+  <si>
+    <t>nauru</t>
+  </si>
+  <si>
+    <t>nepal</t>
+  </si>
+  <si>
+    <t>niger</t>
+  </si>
+  <si>
+    <t>nigeria</t>
+  </si>
+  <si>
+    <t>netherlands</t>
+  </si>
+  <si>
+    <t>nicaragua</t>
+  </si>
+  <si>
+    <t>new zealand</t>
+  </si>
+  <si>
+    <t>norway</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> uae </t>
+  </si>
+  <si>
+    <t>oman</t>
+  </si>
+  <si>
+    <t>pakistan</t>
+  </si>
+  <si>
+    <t>palau</t>
+  </si>
+  <si>
+    <t>palestine</t>
+  </si>
+  <si>
+    <t>panama</t>
+  </si>
+  <si>
+    <t>papua new guinea</t>
+  </si>
+  <si>
+    <t>paraguay</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> peru </t>
+  </si>
+  <si>
+    <t>poland</t>
+  </si>
+  <si>
+    <t>portugal</t>
+  </si>
+  <si>
+    <t>rwanda</t>
+  </si>
+  <si>
+    <t>romania</t>
+  </si>
+  <si>
+    <t>el salvador</t>
+  </si>
+  <si>
+    <t>samoa</t>
+  </si>
+  <si>
+    <t>san marino</t>
+  </si>
+  <si>
+    <t>são tomé príncipe</t>
+  </si>
+  <si>
+    <t>saudi arabia</t>
+  </si>
+  <si>
+    <t>seychelles</t>
+  </si>
+  <si>
+    <t>senegal</t>
+  </si>
+  <si>
+    <t>saint vincent of the grenadines</t>
+  </si>
+  <si>
+    <t>saint kittsey nevis</t>
+  </si>
+  <si>
+    <t>saint lucia</t>
+  </si>
+  <si>
+    <t>serbia</t>
+  </si>
+  <si>
+    <t>singapore</t>
+  </si>
+  <si>
+    <t>syria</t>
+  </si>
+  <si>
+    <t>slovakia</t>
+  </si>
+  <si>
+    <t>slovenia</t>
+  </si>
+  <si>
+    <t>solomon islands</t>
+  </si>
+  <si>
+    <t>somalia</t>
+  </si>
+  <si>
+    <t>sudan</t>
+  </si>
+  <si>
+    <t>suriname</t>
+  </si>
+  <si>
+    <t>sierra leone</t>
+  </si>
+  <si>
+    <t>thailand</t>
+  </si>
+  <si>
+    <t>tanzania</t>
+  </si>
+  <si>
+    <t>togo</t>
+  </si>
+  <si>
+    <t>tonga</t>
+  </si>
+  <si>
+    <t>trinidad and tobago</t>
+  </si>
+  <si>
+    <t>tuvalu</t>
+  </si>
+  <si>
+    <t>tunisia</t>
+  </si>
+  <si>
+    <t>turkmenistan</t>
+  </si>
+  <si>
+    <t>turkey</t>
+  </si>
+  <si>
+    <t>uganda</t>
+  </si>
+  <si>
+    <t>uzbekistan</t>
+  </si>
+  <si>
+    <t>ukraine</t>
+  </si>
+  <si>
+    <t>uruguay</t>
+  </si>
+  <si>
+    <t>federated states of micronesia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fiji </t>
+  </si>
+  <si>
+    <t>philippines</t>
+  </si>
+  <si>
+    <t>finland</t>
+  </si>
+  <si>
+    <t>france</t>
+  </si>
+  <si>
+    <t>croatia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> car </t>
+  </si>
+  <si>
+    <t>chad</t>
+  </si>
+  <si>
+    <t>montenegro</t>
+  </si>
+  <si>
+    <t>czech republic</t>
+  </si>
+  <si>
+    <t>chile</t>
+  </si>
+  <si>
+    <t>switzerland</t>
+  </si>
+  <si>
+    <t>sweden</t>
+  </si>
+  <si>
+    <t>sri lanka</t>
+  </si>
+  <si>
+    <t>ecuador</t>
+  </si>
+  <si>
+    <t>equatorial guinea</t>
+  </si>
+  <si>
+    <t>eritrea</t>
+  </si>
+  <si>
+    <t>eswatini</t>
+  </si>
+  <si>
+    <t>estonia</t>
+  </si>
+  <si>
+    <t>ethiopia</t>
+  </si>
+  <si>
+    <t>south africa</t>
+  </si>
+  <si>
+    <t>south ossetia</t>
+  </si>
+  <si>
+    <t>south sudan</t>
+  </si>
+  <si>
+    <t>jamaica</t>
+  </si>
+  <si>
+    <t>japan</t>
+  </si>
+  <si>
+    <t>россию</t>
+  </si>
+  <si>
+    <t>Россию</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ссср </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> СССР </t>
+  </si>
+  <si>
+    <t>европу</t>
+  </si>
+  <si>
+    <t>Европу</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3717,6 +5965,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="PT Astra Sans"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="9">
@@ -3862,7 +6117,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3871,6 +6126,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
@@ -4117,7 +6381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B600"/>
+  <dimension ref="A1:B975"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.54296875" customWidth="1"/>
@@ -6232,10 +8496,10 @@
     </row>
     <row r="264" spans="1:2">
       <c r="A264" t="s">
-        <v>1186</v>
+        <v>1144</v>
       </c>
       <c r="B264" t="s">
-        <v>1187</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -7568,18 +9832,18 @@
     </row>
     <row r="431" spans="1:2">
       <c r="A431" t="s">
-        <v>1188</v>
+        <v>1146</v>
       </c>
       <c r="B431" t="s">
-        <v>1189</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="432" spans="1:2">
       <c r="A432" t="s">
-        <v>1190</v>
+        <v>1148</v>
       </c>
       <c r="B432" t="s">
-        <v>1191</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -8040,10 +10304,10 @@
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>1184</v>
+        <v>1142</v>
       </c>
       <c r="B490" t="s">
-        <v>1185</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -8656,274 +10920,3274 @@
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="B567" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="B568" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="569" spans="1:2">
       <c r="A569" t="s">
-        <v>1133</v>
+        <v>1943</v>
       </c>
       <c r="B569" t="s">
-        <v>1134</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="B570" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
-        <v>1126</v>
+        <v>1162</v>
       </c>
       <c r="B571" t="s">
-        <v>1127</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="572" spans="1:2">
       <c r="A572" t="s">
-        <v>1192</v>
+        <v>1945</v>
       </c>
       <c r="B572" t="s">
-        <v>1193</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
-        <v>1194</v>
+        <v>1150</v>
       </c>
       <c r="B573" t="s">
-        <v>1195</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
-        <v>1196</v>
+        <v>1152</v>
       </c>
       <c r="B574" t="s">
-        <v>1197</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>1198</v>
+        <v>1154</v>
       </c>
       <c r="B575" t="s">
-        <v>1199</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="576" spans="1:2">
       <c r="A576" t="s">
-        <v>1128</v>
+        <v>1947</v>
       </c>
       <c r="B576" t="s">
-        <v>1135</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>1136</v>
+        <v>1156</v>
       </c>
       <c r="B577" t="s">
-        <v>1137</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>1138</v>
+        <v>1158</v>
       </c>
       <c r="B578" t="s">
-        <v>1139</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="B579" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B580" t="s">
         <v>1170</v>
-      </c>
-      <c r="B580" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>1172</v>
+        <v>1558</v>
       </c>
       <c r="B581" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>1168</v>
+        <v>1559</v>
       </c>
       <c r="B582" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>1174</v>
+        <v>1560</v>
       </c>
       <c r="B583" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>1176</v>
+        <v>1561</v>
       </c>
       <c r="B584" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
-        <v>1164</v>
+        <v>1562</v>
       </c>
       <c r="B585" t="s">
-        <v>1165</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
-        <v>1140</v>
+        <v>1563</v>
       </c>
       <c r="B586" t="s">
-        <v>1141</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
-        <v>1142</v>
+        <v>1564</v>
       </c>
       <c r="B587" t="s">
-        <v>1143</v>
-      </c>
-    </row>
-    <row r="588" spans="1:2">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2" ht="30">
       <c r="A588" t="s">
-        <v>1144</v>
+        <v>1565</v>
       </c>
       <c r="B588" t="s">
-        <v>1145</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
-        <v>1156</v>
+        <v>1566</v>
       </c>
       <c r="B589" t="s">
-        <v>1157</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" t="s">
-        <v>1158</v>
+        <v>1168</v>
       </c>
       <c r="B590" t="s">
-        <v>1159</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
-        <v>1146</v>
+        <v>1567</v>
       </c>
       <c r="B591" t="s">
-        <v>1147</v>
-      </c>
-    </row>
-    <row r="592" spans="1:2">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2" ht="30">
       <c r="A592" t="s">
-        <v>1148</v>
+        <v>1568</v>
       </c>
       <c r="B592" t="s">
-        <v>1149</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" t="s">
-        <v>1150</v>
+        <v>1569</v>
       </c>
       <c r="B593" t="s">
-        <v>1151</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>1152</v>
+        <v>1570</v>
       </c>
       <c r="B594" t="s">
-        <v>1153</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
-        <v>1154</v>
+        <v>1571</v>
       </c>
       <c r="B595" t="s">
-        <v>1155</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
-        <v>1160</v>
+        <v>1572</v>
       </c>
       <c r="B596" t="s">
-        <v>1161</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
-        <v>1162</v>
+        <v>1573</v>
       </c>
       <c r="B597" t="s">
-        <v>1163</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
-        <v>1178</v>
+        <v>1574</v>
       </c>
       <c r="B598" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
-        <v>1180</v>
+        <v>1575</v>
       </c>
       <c r="B599" t="s">
-        <v>1183</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
-        <v>1181</v>
+        <v>1576</v>
       </c>
       <c r="B600" t="s">
-        <v>1182</v>
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B601" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2" ht="30">
+      <c r="A602" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B602" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B603" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B604" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B605" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B606" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B607" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B608" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B609" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B610" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B611" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B612" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B613" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B614" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B615" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B616" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B617" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B618" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B619" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B620" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B621" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B622" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B623" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B624" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2">
+      <c r="A625" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B625" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2">
+      <c r="A626" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B626" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2">
+      <c r="A627" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B627" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2">
+      <c r="A628" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B628" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2">
+      <c r="A629" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B629" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2">
+      <c r="A630" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B630" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2">
+      <c r="A631" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B631" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2" ht="30">
+      <c r="A632" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B632" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2" ht="30">
+      <c r="A633" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B633" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2">
+      <c r="A634" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B634" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2">
+      <c r="A635" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B635" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B636" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2">
+      <c r="A637" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B637" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2">
+      <c r="A638" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B638" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2">
+      <c r="A639" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B639" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B640" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B641" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B642" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2">
+      <c r="A643" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B643" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2">
+      <c r="A644" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B644" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2">
+      <c r="A645" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B645" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B646" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2">
+      <c r="A647" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B647" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2">
+      <c r="A648" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B648" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2">
+      <c r="A649" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B649" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B650" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B651" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B652" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B653" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B654" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B655" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B656" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B657" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B658" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B659" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B660" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2">
+      <c r="A661" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B661" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2">
+      <c r="A662" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B662" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B663" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2" ht="30">
+      <c r="A664" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B664" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B665" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B666" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B667" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B668" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2">
+      <c r="A669" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B669" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2">
+      <c r="A670" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B670" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2">
+      <c r="A671" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B671" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2">
+      <c r="A672" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B672" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B673" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2">
+      <c r="A674" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B674" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2">
+      <c r="A675" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B675" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B676" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B677" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B678" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2">
+      <c r="A679" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B679" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2">
+      <c r="A680" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B680" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2" ht="30">
+      <c r="A681" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B681" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2">
+      <c r="A682" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B682" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2">
+      <c r="A683" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B683" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2">
+      <c r="A684" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B684" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2">
+      <c r="A685" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B685" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2">
+      <c r="A686" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B686" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2" ht="30">
+      <c r="A687" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B687" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2">
+      <c r="A688" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B688" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2" ht="30">
+      <c r="A689" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B689" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2">
+      <c r="A690" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B690" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2">
+      <c r="A691" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B691" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2">
+      <c r="A692" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B692" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2">
+      <c r="A693" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B693" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2">
+      <c r="A694" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B694" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2">
+      <c r="A695" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B695" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2">
+      <c r="A696" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B696" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2">
+      <c r="A697" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B697" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2">
+      <c r="A698" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B698" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2">
+      <c r="A699" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B699" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2">
+      <c r="A700" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B700" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2">
+      <c r="A701" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B701" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2">
+      <c r="A702" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B702" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2">
+      <c r="A703" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B703" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2">
+      <c r="A704" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B704" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2">
+      <c r="A705" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B705" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2">
+      <c r="A706" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B706" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2">
+      <c r="A707" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B707" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2">
+      <c r="A708" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B708" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2">
+      <c r="A709" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B709" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2">
+      <c r="A710" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B710" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2" ht="30">
+      <c r="A711" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B711" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2">
+      <c r="A712" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B712" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2">
+      <c r="A713" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B713" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2">
+      <c r="A714" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B714" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2">
+      <c r="A715" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B715" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2">
+      <c r="A716" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B716" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2">
+      <c r="A717" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B717" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2">
+      <c r="A718" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B718" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2">
+      <c r="A719" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B719" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2">
+      <c r="A720" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B720" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2" ht="30">
+      <c r="A721" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B721" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2" ht="30">
+      <c r="A722" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B722" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2" ht="30">
+      <c r="A723" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B723" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2">
+      <c r="A724" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B724" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2" ht="30">
+      <c r="A725" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B725" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2">
+      <c r="A726" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B726" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2">
+      <c r="A727" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B727" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2">
+      <c r="A728" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B728" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2">
+      <c r="A729" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B729" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2">
+      <c r="A730" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B730" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2">
+      <c r="A731" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B731" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2">
+      <c r="A732" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B732" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2" ht="30">
+      <c r="A733" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B733" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2">
+      <c r="A734" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B734" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2">
+      <c r="A735" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B735" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2">
+      <c r="A736" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B736" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2">
+      <c r="A737" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B737" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2">
+      <c r="A738" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B738" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2">
+      <c r="A739" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B739" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2">
+      <c r="A740" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B740" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2">
+      <c r="A741" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B741" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2">
+      <c r="A742" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B742" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2">
+      <c r="A743" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B743" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2" ht="30">
+      <c r="A744" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B744" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2">
+      <c r="A745" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B745" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2">
+      <c r="A746" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B746" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2">
+      <c r="A747" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B747" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2">
+      <c r="A748" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B748" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2">
+      <c r="A749" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B749" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2">
+      <c r="A750" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B750" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2">
+      <c r="A751" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B751" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2">
+      <c r="A752" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B752" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2" ht="45">
+      <c r="A753" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B753" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2">
+      <c r="A754" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B754" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2">
+      <c r="A755" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B755" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2">
+      <c r="A756" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B756" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2">
+      <c r="A757" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B757" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2">
+      <c r="A758" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B758" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2">
+      <c r="A759" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B759" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2">
+      <c r="A760" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B760" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2">
+      <c r="A761" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B761" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2">
+      <c r="A762" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B762" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2">
+      <c r="A763" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B763" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2">
+      <c r="A764" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B764" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2">
+      <c r="A765" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B765" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2">
+      <c r="A766" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B766" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2">
+      <c r="A767" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B767" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2" ht="30">
+      <c r="A768" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B768" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2">
+      <c r="A769" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B769" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2">
+      <c r="A770" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B770" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2">
+      <c r="A771" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B771" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2">
+      <c r="A772" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B772" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2">
+      <c r="A773" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B773" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2">
+      <c r="A774" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B774" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2">
+      <c r="A775" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B775" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2">
+      <c r="A776" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B776" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2">
+      <c r="A777" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B777" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2">
+      <c r="A778" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B778" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2">
+      <c r="A779" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B779" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2">
+      <c r="A780" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B780" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2">
+      <c r="A781" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B781" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2">
+      <c r="A782" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B782" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2">
+      <c r="A783" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B783" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2">
+      <c r="A784" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B784" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2">
+      <c r="A785" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B785" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2" ht="30">
+      <c r="A786" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B786" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2">
+      <c r="A787" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B787" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2">
+      <c r="A788" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B788" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2">
+      <c r="A789" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B789" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2">
+      <c r="A790" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B790" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2">
+      <c r="A791" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B791" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2">
+      <c r="A792" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B792" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2">
+      <c r="A793" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B793" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2">
+      <c r="A794" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B794" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2">
+      <c r="A795" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B795" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2">
+      <c r="A796" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B796" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2">
+      <c r="A797" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B797" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2">
+      <c r="A798" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B798" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2">
+      <c r="A799" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B799" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2" ht="30">
+      <c r="A800" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B800" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2">
+      <c r="A801" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B801" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2">
+      <c r="A802" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B802" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2">
+      <c r="A803" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B803" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2">
+      <c r="A804" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B804" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2">
+      <c r="A805" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B805" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2">
+      <c r="A806" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B806" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2">
+      <c r="A807" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B807" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2">
+      <c r="A808" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B808" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2">
+      <c r="A809" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B809" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2">
+      <c r="A810" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B810" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2">
+      <c r="A811" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B811" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2">
+      <c r="A812" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B812" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2">
+      <c r="A813" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B813" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2">
+      <c r="A814" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B814" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2">
+      <c r="A815" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B815" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2">
+      <c r="A816" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B816" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2">
+      <c r="A817" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B817" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2">
+      <c r="A818" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B818" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2">
+      <c r="A819" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B819" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="820" spans="1:2">
+      <c r="A820" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B820" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="821" spans="1:2">
+      <c r="A821" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B821" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="822" spans="1:2">
+      <c r="A822" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B822" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="823" spans="1:2">
+      <c r="A823" t="s">
+        <v>1792</v>
+      </c>
+      <c r="B823" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="824" spans="1:2">
+      <c r="A824" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B824" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="825" spans="1:2">
+      <c r="A825" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B825" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="826" spans="1:2">
+      <c r="A826" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B826" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="827" spans="1:2">
+      <c r="A827" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B827" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="828" spans="1:2">
+      <c r="A828" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B828" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="829" spans="1:2">
+      <c r="A829" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B829" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="830" spans="1:2">
+      <c r="A830" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B830" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="831" spans="1:2">
+      <c r="A831" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B831" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="832" spans="1:2">
+      <c r="A832" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B832" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="833" spans="1:2">
+      <c r="A833" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B833" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="834" spans="1:2">
+      <c r="A834" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B834" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="835" spans="1:2">
+      <c r="A835" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B835" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="836" spans="1:2">
+      <c r="A836" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B836" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="837" spans="1:2">
+      <c r="A837" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B837" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="838" spans="1:2">
+      <c r="A838" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B838" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="839" spans="1:2">
+      <c r="A839" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B839" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="840" spans="1:2">
+      <c r="A840" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B840" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="841" spans="1:2">
+      <c r="A841" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B841" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="842" spans="1:2">
+      <c r="A842" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B842" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="843" spans="1:2">
+      <c r="A843" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B843" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="844" spans="1:2">
+      <c r="A844" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B844" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="845" spans="1:2">
+      <c r="A845" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B845" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="846" spans="1:2">
+      <c r="A846" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B846" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="847" spans="1:2">
+      <c r="A847" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B847" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="848" spans="1:2">
+      <c r="A848" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B848" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="849" spans="1:2">
+      <c r="A849" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B849" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="850" spans="1:2">
+      <c r="A850" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B850" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="851" spans="1:2">
+      <c r="A851" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B851" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="852" spans="1:2">
+      <c r="A852" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B852" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="853" spans="1:2">
+      <c r="A853" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B853" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="854" spans="1:2">
+      <c r="A854" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B854" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="855" spans="1:2">
+      <c r="A855" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B855" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="856" spans="1:2">
+      <c r="A856" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B856" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="857" spans="1:2">
+      <c r="A857" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B857" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="858" spans="1:2">
+      <c r="A858" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B858" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="859" spans="1:2">
+      <c r="A859" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B859" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="860" spans="1:2" ht="30">
+      <c r="A860" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B860" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="861" spans="1:2">
+      <c r="A861" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B861" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="862" spans="1:2">
+      <c r="A862" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B862" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="863" spans="1:2">
+      <c r="A863" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B863" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="864" spans="1:2">
+      <c r="A864" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B864" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="865" spans="1:2">
+      <c r="A865" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B865" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="866" spans="1:2">
+      <c r="A866" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B866" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="867" spans="1:2">
+      <c r="A867" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B867" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="868" spans="1:2">
+      <c r="A868" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B868" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="869" spans="1:2">
+      <c r="A869" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B869" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="870" spans="1:2">
+      <c r="A870" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B870" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="871" spans="1:2">
+      <c r="A871" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B871" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="872" spans="1:2">
+      <c r="A872" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B872" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="873" spans="1:2">
+      <c r="A873" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B873" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="874" spans="1:2">
+      <c r="A874" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B874" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="875" spans="1:2">
+      <c r="A875" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B875" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="876" spans="1:2">
+      <c r="A876" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B876" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="877" spans="1:2">
+      <c r="A877" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B877" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="878" spans="1:2">
+      <c r="A878" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B878" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="879" spans="1:2">
+      <c r="A879" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B879" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="880" spans="1:2">
+      <c r="A880" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B880" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="881" spans="1:2">
+      <c r="A881" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B881" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="882" spans="1:2">
+      <c r="A882" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B882" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="883" spans="1:2">
+      <c r="A883" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B883" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="884" spans="1:2">
+      <c r="A884" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B884" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="885" spans="1:2">
+      <c r="A885" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B885" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="886" spans="1:2">
+      <c r="A886" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B886" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="887" spans="1:2">
+      <c r="A887" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B887" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="888" spans="1:2">
+      <c r="A888" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B888" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="889" spans="1:2">
+      <c r="A889" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B889" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="890" spans="1:2">
+      <c r="A890" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B890" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="891" spans="1:2" ht="30">
+      <c r="A891" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B891" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="892" spans="1:2">
+      <c r="A892" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B892" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="893" spans="1:2">
+      <c r="A893" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B893" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="894" spans="1:2">
+      <c r="A894" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B894" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="895" spans="1:2">
+      <c r="A895" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B895" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="896" spans="1:2">
+      <c r="A896" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B896" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="897" spans="1:2">
+      <c r="A897" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B897" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="898" spans="1:2">
+      <c r="A898" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B898" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="899" spans="1:2">
+      <c r="A899" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B899" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="900" spans="1:2">
+      <c r="A900" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B900" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="901" spans="1:2">
+      <c r="A901" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B901" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="902" spans="1:2">
+      <c r="A902" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B902" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="903" spans="1:2">
+      <c r="A903" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B903" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="904" spans="1:2">
+      <c r="A904" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B904" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="905" spans="1:2">
+      <c r="A905" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B905" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="906" spans="1:2">
+      <c r="A906" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B906" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="907" spans="1:2">
+      <c r="A907" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B907" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="908" spans="1:2">
+      <c r="A908" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B908" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="909" spans="1:2">
+      <c r="A909" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B909" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="910" spans="1:2">
+      <c r="A910" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B910" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="911" spans="1:2">
+      <c r="A911" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B911" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="912" spans="1:2">
+      <c r="A912" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B912" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="913" spans="1:2">
+      <c r="A913" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B913" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="914" spans="1:2">
+      <c r="A914" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B914" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="915" spans="1:2">
+      <c r="A915" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B915" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="916" spans="1:2">
+      <c r="A916" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B916" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="917" spans="1:2">
+      <c r="A917" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B917" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="918" spans="1:2">
+      <c r="A918" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B918" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="919" spans="1:2">
+      <c r="A919" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B919" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="920" spans="1:2">
+      <c r="A920" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B920" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="921" spans="1:2">
+      <c r="A921" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B921" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="922" spans="1:2">
+      <c r="A922" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B922" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="923" spans="1:2" ht="30">
+      <c r="A923" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B923" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="924" spans="1:2">
+      <c r="A924" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B924" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="925" spans="1:2">
+      <c r="A925" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B925" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="926" spans="1:2">
+      <c r="A926" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B926" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="927" spans="1:2">
+      <c r="A927" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B927" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="928" spans="1:2">
+      <c r="A928" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B928" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="929" spans="1:2">
+      <c r="A929" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B929" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="930" spans="1:2">
+      <c r="A930" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B930" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="931" spans="1:2">
+      <c r="A931" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B931" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="932" spans="1:2">
+      <c r="A932" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B932" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="933" spans="1:2">
+      <c r="A933" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B933" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="934" spans="1:2">
+      <c r="A934" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B934" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="935" spans="1:2">
+      <c r="A935" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B935" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="936" spans="1:2">
+      <c r="A936" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B936" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="937" spans="1:2">
+      <c r="A937" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B937" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="938" spans="1:2">
+      <c r="A938" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B938" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="939" spans="1:2">
+      <c r="A939" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B939" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="940" spans="1:2">
+      <c r="A940" t="s">
+        <v>1907</v>
+      </c>
+      <c r="B940" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="941" spans="1:2">
+      <c r="A941" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B941" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="942" spans="1:2" ht="30">
+      <c r="A942" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B942" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="943" spans="1:2">
+      <c r="A943" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B943" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="944" spans="1:2">
+      <c r="A944" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B944" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="945" spans="1:2">
+      <c r="A945" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B945" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="946" spans="1:2">
+      <c r="A946" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B946" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="947" spans="1:2">
+      <c r="A947" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B947" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="948" spans="1:2">
+      <c r="A948" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B948" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="949" spans="1:2">
+      <c r="A949" t="s">
+        <v>1916</v>
+      </c>
+      <c r="B949" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="950" spans="1:2">
+      <c r="A950" t="s">
+        <v>1917</v>
+      </c>
+      <c r="B950" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="951" spans="1:2" ht="30">
+      <c r="A951" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B951" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="952" spans="1:2">
+      <c r="A952" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B952" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="953" spans="1:2">
+      <c r="A953" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B953" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="954" spans="1:2">
+      <c r="A954" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B954" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="955" spans="1:2">
+      <c r="A955" t="s">
+        <v>1922</v>
+      </c>
+      <c r="B955" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="956" spans="1:2">
+      <c r="A956" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B956" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="957" spans="1:2">
+      <c r="A957" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B957" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="958" spans="1:2">
+      <c r="A958" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B958" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="959" spans="1:2">
+      <c r="A959" t="s">
+        <v>1926</v>
+      </c>
+      <c r="B959" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="960" spans="1:2">
+      <c r="A960" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B960" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="961" spans="1:2">
+      <c r="A961" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B961" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="962" spans="1:2">
+      <c r="A962" t="s">
+        <v>1929</v>
+      </c>
+      <c r="B962" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="963" spans="1:2">
+      <c r="A963" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B963" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="964" spans="1:2">
+      <c r="A964" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B964" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="965" spans="1:2">
+      <c r="A965" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B965" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="966" spans="1:2">
+      <c r="A966" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B966" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="967" spans="1:2">
+      <c r="A967" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B967" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="968" spans="1:2">
+      <c r="A968" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B968" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="969" spans="1:2">
+      <c r="A969" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B969" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="970" spans="1:2">
+      <c r="A970" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B970" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="971" spans="1:2">
+      <c r="A971" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B971" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="972" spans="1:2">
+      <c r="A972" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B972" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="973" spans="1:2">
+      <c r="A973" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B973" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="974" spans="1:2">
+      <c r="A974" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B974" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="975" spans="1:2">
+      <c r="A975" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B975" t="s">
+        <v>1548</v>
       </c>
     </row>
   </sheetData>
@@ -8933,4 +14197,3783 @@
   <pageMargins left="0.39370078740157477" right="0.39370078740157477" top="0.78740157480314954" bottom="0.78740157480314954" header="0.39370078740157477" footer="0.39370078740157477"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A65946C6-7FD4-4942-A604-CD9F140207A6}">
+  <dimension ref="A1:E198"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.08984375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="31.08984375" customWidth="1"/>
+    <col min="3" max="4" width="23.1796875" customWidth="1"/>
+    <col min="5" max="5" width="25.26953125" customWidth="1"/>
+    <col min="6" max="6" width="25.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="19.2">
+      <c r="A1" s="3" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C1" t="str">
+        <f>LOWER(A1)</f>
+        <v>абхазия</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E1" t="str">
+        <f>LOWER(D1)</f>
+        <v>abkhazia</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="19.2">
+      <c r="A2" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C2" t="str">
+        <f t="shared" ref="C2:C65" si="0">LOWER(A2)</f>
+        <v>австралия</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E2" t="str">
+        <f t="shared" ref="E2:E65" si="1">LOWER(D2)</f>
+        <v>australia</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="19.2">
+      <c r="A3" s="3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C3" t="str">
+        <f t="shared" si="0"/>
+        <v>австрия</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E3" t="str">
+        <f t="shared" si="1"/>
+        <v>austria</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="19.2">
+      <c r="A4" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v>азербайджан</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E4" t="str">
+        <f t="shared" si="1"/>
+        <v>azerbaijan</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="19.2">
+      <c r="A5" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v>албания</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E5" t="str">
+        <f t="shared" si="1"/>
+        <v>albania</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="19.2">
+      <c r="A6" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v>алжир</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>1365</v>
+      </c>
+      <c r="E6" t="str">
+        <f t="shared" si="1"/>
+        <v>algeria</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="19.2">
+      <c r="A7" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v>ангола</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" si="1"/>
+        <v>angola</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="19.2">
+      <c r="A8" s="3" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v>андорра</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="1"/>
+        <v>andorra</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="19.2">
+      <c r="A9" s="3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="0"/>
+        <v>антигуа и барбуда</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="1"/>
+        <v>antigua and barbuda</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="19.2">
+      <c r="A10" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="0"/>
+        <v>аргентина</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E10" t="str">
+        <f t="shared" si="1"/>
+        <v>argentina</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="19.2">
+      <c r="A11" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="0"/>
+        <v>армения</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E11" t="str">
+        <f t="shared" si="1"/>
+        <v>armenia</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="19.2">
+      <c r="A12" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="0"/>
+        <v>афганистан</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E12" t="str">
+        <f t="shared" si="1"/>
+        <v>afghanistan</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="19.2">
+      <c r="A13" s="3" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="0"/>
+        <v>багамские острова</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E13" t="str">
+        <f t="shared" si="1"/>
+        <v>bahamas</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="19.2">
+      <c r="A14" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" si="0"/>
+        <v>бангладеш</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E14" t="str">
+        <f t="shared" si="1"/>
+        <v>bangladesh</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="19.2">
+      <c r="A15" s="3" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C15" t="str">
+        <f t="shared" si="0"/>
+        <v>барбадос</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E15" t="str">
+        <f t="shared" si="1"/>
+        <v>barbados</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="19.2">
+      <c r="A16" s="3" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="0"/>
+        <v>бахрейн</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E16" t="str">
+        <f t="shared" si="1"/>
+        <v>bahrain</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="19.2">
+      <c r="A17" s="3" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v>белиз</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E17" t="str">
+        <f t="shared" si="1"/>
+        <v>belize</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="19.2">
+      <c r="A18" s="3" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v>белоруссия</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E18" t="str">
+        <f t="shared" si="1"/>
+        <v>belarus</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="19.2">
+      <c r="A19" s="3" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v>бельгия</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E19" t="str">
+        <f t="shared" si="1"/>
+        <v>belgium</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="19.2">
+      <c r="A20" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v>бенин</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E20" t="str">
+        <f t="shared" si="1"/>
+        <v>benin</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="19.2">
+      <c r="A21" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C21" t="str">
+        <f t="shared" si="0"/>
+        <v>болгария</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>1380</v>
+      </c>
+      <c r="E21" t="str">
+        <f t="shared" si="1"/>
+        <v>bulgaria</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="19.2">
+      <c r="A22" s="3" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C22" t="str">
+        <f t="shared" si="0"/>
+        <v>боливия</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>1381</v>
+      </c>
+      <c r="E22" t="str">
+        <f t="shared" si="1"/>
+        <v>bolivia</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="19.2">
+      <c r="A23" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C23" t="str">
+        <f t="shared" si="0"/>
+        <v>босния и герцеговина</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>1382</v>
+      </c>
+      <c r="E23" t="str">
+        <f t="shared" si="1"/>
+        <v>bosnia and herzegovina</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="19.2">
+      <c r="A24" s="3" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C24" t="str">
+        <f t="shared" si="0"/>
+        <v>ботсвана</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E24" t="str">
+        <f t="shared" si="1"/>
+        <v>botswana</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="19.2">
+      <c r="A25" s="3" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C25" t="str">
+        <f t="shared" si="0"/>
+        <v>бразилия</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E25" t="str">
+        <f t="shared" si="1"/>
+        <v>brazil</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="19.2">
+      <c r="A26" s="3" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="0"/>
+        <v>бруней</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E26" t="str">
+        <f t="shared" si="1"/>
+        <v>brunei</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="19.2">
+      <c r="A27" s="3" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C27" t="str">
+        <f t="shared" si="0"/>
+        <v>буркина-фасо</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>1386</v>
+      </c>
+      <c r="E27" t="str">
+        <f t="shared" si="1"/>
+        <v>burkina faso</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="19.2">
+      <c r="A28" s="3" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C28" t="str">
+        <f t="shared" si="0"/>
+        <v>бурунди</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E28" t="str">
+        <f t="shared" si="1"/>
+        <v>burundi</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="19.2">
+      <c r="A29" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C29" t="str">
+        <f t="shared" si="0"/>
+        <v>бутан</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>1388</v>
+      </c>
+      <c r="E29" t="str">
+        <f t="shared" si="1"/>
+        <v>bhutan</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="19.2">
+      <c r="A30" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C30" t="str">
+        <f t="shared" si="0"/>
+        <v>вануату</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E30" t="str">
+        <f t="shared" si="1"/>
+        <v>vanuatu</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="19.2">
+      <c r="A31" s="3" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C31" t="str">
+        <f t="shared" si="0"/>
+        <v>ватикан</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E31" t="str">
+        <f t="shared" si="1"/>
+        <v>vatican city</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="19.2">
+      <c r="A32" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C32" t="str">
+        <f t="shared" si="0"/>
+        <v>великобритания</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>1391</v>
+      </c>
+      <c r="E32" t="str">
+        <f t="shared" si="1"/>
+        <v>united kingdom</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="19.2">
+      <c r="A33" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C33" t="str">
+        <f t="shared" si="0"/>
+        <v>венгрия</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E33" t="str">
+        <f t="shared" si="1"/>
+        <v>hungary</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="19.2">
+      <c r="A34" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C34" t="str">
+        <f t="shared" si="0"/>
+        <v>венесуэла</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E34" t="str">
+        <f t="shared" si="1"/>
+        <v>venezuela</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="19.2">
+      <c r="A35" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C35" t="str">
+        <f t="shared" si="0"/>
+        <v>восточный тимор</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>1394</v>
+      </c>
+      <c r="E35" t="str">
+        <f t="shared" si="1"/>
+        <v>east timor</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="19.2">
+      <c r="A36" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C36" t="str">
+        <f t="shared" si="0"/>
+        <v>вьетнам</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E36" t="str">
+        <f t="shared" si="1"/>
+        <v>vietnam</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="19.2">
+      <c r="A37" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C37" t="str">
+        <f t="shared" si="0"/>
+        <v>габон</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E37" t="str">
+        <f t="shared" si="1"/>
+        <v>gabon</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="19.2">
+      <c r="A38" s="3" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C38" t="str">
+        <f t="shared" si="0"/>
+        <v>гаити</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E38" t="str">
+        <f t="shared" si="1"/>
+        <v>haiti</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="19.2">
+      <c r="A39" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C39" t="str">
+        <f t="shared" si="0"/>
+        <v>гайана</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>1398</v>
+      </c>
+      <c r="E39" t="str">
+        <f t="shared" si="1"/>
+        <v>guyana</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="19.2">
+      <c r="A40" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" si="0"/>
+        <v>гамбия</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E40" t="str">
+        <f t="shared" si="1"/>
+        <v>gambia</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="19.2">
+      <c r="A41" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C41" t="str">
+        <f t="shared" si="0"/>
+        <v>гана</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E41" t="str">
+        <f t="shared" si="1"/>
+        <v>ghana</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="19.2">
+      <c r="A42" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" si="0"/>
+        <v>гватемала</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E42" t="str">
+        <f t="shared" si="1"/>
+        <v>guatemala</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="19.2">
+      <c r="A43" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C43" t="str">
+        <f t="shared" si="0"/>
+        <v>гвинея</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="E43" t="str">
+        <f t="shared" si="1"/>
+        <v>guinea</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="19.2">
+      <c r="A44" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C44" t="str">
+        <f t="shared" si="0"/>
+        <v>гвинея-бисау</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E44" t="str">
+        <f t="shared" si="1"/>
+        <v>guinea-bissau</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="19.2">
+      <c r="A45" s="3" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C45" t="str">
+        <f t="shared" si="0"/>
+        <v>германия</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E45" t="str">
+        <f t="shared" si="1"/>
+        <v>germany</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="19.2">
+      <c r="A46" s="3" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="0"/>
+        <v>гондурас</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E46" t="str">
+        <f t="shared" si="1"/>
+        <v>honduras</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="19.2">
+      <c r="A47" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="0"/>
+        <v>гренада</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>1406</v>
+      </c>
+      <c r="E47" t="str">
+        <f t="shared" si="1"/>
+        <v>grenada</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="19.2">
+      <c r="A48" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" si="0"/>
+        <v>греция</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>1407</v>
+      </c>
+      <c r="E48" t="str">
+        <f t="shared" si="1"/>
+        <v>greece</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="19.2">
+      <c r="A49" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C49" t="str">
+        <f t="shared" si="0"/>
+        <v>грузия</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="E49" t="str">
+        <f t="shared" si="1"/>
+        <v>georgia</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="19.2">
+      <c r="A50" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="0"/>
+        <v>дания</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>1409</v>
+      </c>
+      <c r="E50" t="str">
+        <f t="shared" si="1"/>
+        <v>denmark</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="19.2">
+      <c r="A51" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C51" t="str">
+        <f t="shared" si="0"/>
+        <v>джибути</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>1410</v>
+      </c>
+      <c r="E51" t="str">
+        <f t="shared" si="1"/>
+        <v>djibouti</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="19.2">
+      <c r="A52" s="3" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C52" t="str">
+        <f t="shared" si="0"/>
+        <v>доминика</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E52" t="str">
+        <f t="shared" si="1"/>
+        <v>dominica</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="30">
+      <c r="A53" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C53" t="str">
+        <f t="shared" si="0"/>
+        <v>доминиканская республика</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="E53" t="str">
+        <f t="shared" si="1"/>
+        <v>dominican republic</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="19.2">
+      <c r="A54" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C54" t="str">
+        <f t="shared" si="0"/>
+        <v>европейский союз</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E54" t="str">
+        <f t="shared" si="1"/>
+        <v>european union</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="19.2">
+      <c r="A55" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C55" t="str">
+        <f t="shared" si="0"/>
+        <v>египет</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>1414</v>
+      </c>
+      <c r="E55" t="str">
+        <f t="shared" si="1"/>
+        <v>egypt</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="19.2">
+      <c r="A56" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C56" t="str">
+        <f t="shared" si="0"/>
+        <v>замбия</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>1415</v>
+      </c>
+      <c r="E56" t="str">
+        <f t="shared" si="1"/>
+        <v>zambia</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="19.2">
+      <c r="A57" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C57" t="str">
+        <f t="shared" si="0"/>
+        <v>зимбабве</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>1416</v>
+      </c>
+      <c r="E57" t="str">
+        <f t="shared" si="1"/>
+        <v>zimbabwe</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="19.2">
+      <c r="A58" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C58" t="str">
+        <f t="shared" si="0"/>
+        <v>израиль</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E58" t="str">
+        <f t="shared" si="1"/>
+        <v>israel</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="19.2">
+      <c r="A59" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C59" t="str">
+        <f t="shared" si="0"/>
+        <v>индия</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E59" t="str">
+        <f t="shared" si="1"/>
+        <v>india</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="19.2">
+      <c r="A60" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C60" t="str">
+        <f t="shared" si="0"/>
+        <v>индонезия</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="E60" t="str">
+        <f t="shared" si="1"/>
+        <v>indonesia</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="19.2">
+      <c r="A61" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C61" t="str">
+        <f t="shared" si="0"/>
+        <v>иордания</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>1420</v>
+      </c>
+      <c r="E61" t="str">
+        <f t="shared" si="1"/>
+        <v>jordan</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="19.2">
+      <c r="A62" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C62" t="str">
+        <f t="shared" si="0"/>
+        <v>ирак</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E62" t="str">
+        <f t="shared" si="1"/>
+        <v>iraq</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="19.2">
+      <c r="A63" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C63" t="str">
+        <f t="shared" si="0"/>
+        <v>иран</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E63" t="str">
+        <f t="shared" si="1"/>
+        <v>iran</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="19.2">
+      <c r="A64" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C64" t="str">
+        <f t="shared" si="0"/>
+        <v>ирландия</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E64" t="str">
+        <f t="shared" si="1"/>
+        <v>ireland</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="19.2">
+      <c r="A65" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C65" t="str">
+        <f t="shared" si="0"/>
+        <v>исландия</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>1424</v>
+      </c>
+      <c r="E65" t="str">
+        <f t="shared" si="1"/>
+        <v>iceland</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="19.2">
+      <c r="A66" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C66" t="str">
+        <f t="shared" ref="C66:C129" si="2">LOWER(A66)</f>
+        <v>испания</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E66" t="str">
+        <f t="shared" ref="E66:E129" si="3">LOWER(D66)</f>
+        <v>spain</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="19.2">
+      <c r="A67" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C67" t="str">
+        <f t="shared" si="2"/>
+        <v>италия</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E67" t="str">
+        <f t="shared" si="3"/>
+        <v>italy</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="19.2">
+      <c r="A68" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C68" t="str">
+        <f t="shared" si="2"/>
+        <v>йемен</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E68" t="str">
+        <f t="shared" si="3"/>
+        <v>yemen</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="19.2">
+      <c r="A69" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C69" t="str">
+        <f t="shared" si="2"/>
+        <v>кабо-верде</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>1428</v>
+      </c>
+      <c r="E69" t="str">
+        <f t="shared" si="3"/>
+        <v>cape verde</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="19.2">
+      <c r="A70" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C70" t="str">
+        <f t="shared" si="2"/>
+        <v>казахстан</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E70" t="str">
+        <f t="shared" si="3"/>
+        <v>kazakhstan</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="19.2">
+      <c r="A71" s="3" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C71" t="str">
+        <f t="shared" si="2"/>
+        <v>камбоджа</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>1430</v>
+      </c>
+      <c r="E71" t="str">
+        <f t="shared" si="3"/>
+        <v>cambodia</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="19.2">
+      <c r="A72" s="3" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C72" t="str">
+        <f t="shared" si="2"/>
+        <v>камерун</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E72" t="str">
+        <f t="shared" si="3"/>
+        <v>cameroon</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="19.2">
+      <c r="A73" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C73" t="str">
+        <f t="shared" si="2"/>
+        <v>канада</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>1432</v>
+      </c>
+      <c r="E73" t="str">
+        <f t="shared" si="3"/>
+        <v>canada</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="19.2">
+      <c r="A74" s="3" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C74" t="str">
+        <f t="shared" si="2"/>
+        <v>катар</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E74" t="str">
+        <f t="shared" si="3"/>
+        <v>qatar</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="19.2">
+      <c r="A75" s="3" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C75" t="str">
+        <f t="shared" si="2"/>
+        <v>кения</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>1434</v>
+      </c>
+      <c r="E75" t="str">
+        <f t="shared" si="3"/>
+        <v>kenya</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="19.2">
+      <c r="A76" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C76" t="str">
+        <f t="shared" si="2"/>
+        <v>кипр</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E76" t="str">
+        <f t="shared" si="3"/>
+        <v>cyprus</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="19.2">
+      <c r="A77" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C77" t="str">
+        <f t="shared" si="2"/>
+        <v>киргизстан</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E77" t="str">
+        <f t="shared" si="3"/>
+        <v>kyrgyzstan</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="19.2">
+      <c r="A78" s="3" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C78" t="str">
+        <f t="shared" si="2"/>
+        <v>кирибати</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>1437</v>
+      </c>
+      <c r="E78" t="str">
+        <f t="shared" si="3"/>
+        <v>kiribati</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="19.2">
+      <c r="A79" s="3" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C79" t="str">
+        <f t="shared" si="2"/>
+        <v>китай</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E79" t="str">
+        <f t="shared" si="3"/>
+        <v>china</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="19.2">
+      <c r="A80" s="3" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C80" t="str">
+        <f t="shared" si="2"/>
+        <v>колумбия</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E80" t="str">
+        <f t="shared" si="3"/>
+        <v>colombia</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="19.2">
+      <c r="A81" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C81" t="str">
+        <f t="shared" si="2"/>
+        <v>коморы</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="E81" t="str">
+        <f t="shared" si="3"/>
+        <v>comoros</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="19.2">
+      <c r="A82" s="3" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C82" t="str">
+        <f t="shared" si="2"/>
+        <v>дрк (конго)</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E82" t="str">
+        <f t="shared" si="3"/>
+        <v>drc (congo)</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="19.2">
+      <c r="A83" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C83" t="str">
+        <f t="shared" si="2"/>
+        <v>республика конго</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E83" t="str">
+        <f t="shared" si="3"/>
+        <v>republic of the congo</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="19.2">
+      <c r="A84" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C84" t="str">
+        <f t="shared" si="2"/>
+        <v>кндр</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="E84" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> dprk </v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="19.2">
+      <c r="A85" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C85" t="str">
+        <f t="shared" si="2"/>
+        <v>республика корея</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E85" t="str">
+        <f t="shared" si="3"/>
+        <v>republic of korea</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="19.2">
+      <c r="A86" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C86" t="str">
+        <f t="shared" si="2"/>
+        <v>коста-рика</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>1444</v>
+      </c>
+      <c r="E86" t="str">
+        <f t="shared" si="3"/>
+        <v>costa rica</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="19.2">
+      <c r="A87" s="3" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C87" t="str">
+        <f t="shared" si="2"/>
+        <v>кот-д’ивуар</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E87" t="str">
+        <f t="shared" si="3"/>
+        <v>côte d'ivoire</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="19.2">
+      <c r="A88" s="3" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C88" t="str">
+        <f t="shared" si="2"/>
+        <v>куба</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E88" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> cuba </v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="19.2">
+      <c r="A89" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C89" t="str">
+        <f t="shared" si="2"/>
+        <v>кувейт</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E89" t="str">
+        <f t="shared" si="3"/>
+        <v>kuwait</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="19.2">
+      <c r="A90" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C90" t="str">
+        <f t="shared" si="2"/>
+        <v>лаос</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>1554</v>
+      </c>
+      <c r="E90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> laos </v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="19.2">
+      <c r="A91" s="3" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C91" t="str">
+        <f t="shared" si="2"/>
+        <v>латвия</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>1447</v>
+      </c>
+      <c r="E91" t="str">
+        <f t="shared" si="3"/>
+        <v>latvia</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="19.2">
+      <c r="A92" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C92" t="str">
+        <f t="shared" si="2"/>
+        <v>лесото</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="E92" t="str">
+        <f t="shared" si="3"/>
+        <v>lesotho</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="19.2">
+      <c r="A93" s="3" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C93" t="str">
+        <f t="shared" si="2"/>
+        <v>либерия</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="E93" t="str">
+        <f t="shared" si="3"/>
+        <v>liberia</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="19.2">
+      <c r="A94" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C94" t="str">
+        <f t="shared" si="2"/>
+        <v>ливан</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E94" t="str">
+        <f t="shared" si="3"/>
+        <v>lebanon</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="19.2">
+      <c r="A95" s="3" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C95" t="str">
+        <f t="shared" si="2"/>
+        <v>ливия</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>1451</v>
+      </c>
+      <c r="E95" t="str">
+        <f t="shared" si="3"/>
+        <v>libya</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="19.2">
+      <c r="A96" s="3" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C96" t="str">
+        <f t="shared" si="2"/>
+        <v>литва</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E96" t="str">
+        <f t="shared" si="3"/>
+        <v>lithuania</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="19.2">
+      <c r="A97" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C97" t="str">
+        <f t="shared" si="2"/>
+        <v>лихтенштейн</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E97" t="str">
+        <f t="shared" si="3"/>
+        <v>liechtenstein</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="19.2">
+      <c r="A98" s="3" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C98" t="str">
+        <f t="shared" si="2"/>
+        <v>люксембург</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>1454</v>
+      </c>
+      <c r="E98" t="str">
+        <f t="shared" si="3"/>
+        <v>luxembourg</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="19.2">
+      <c r="A99" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C99" t="str">
+        <f t="shared" si="2"/>
+        <v>маврикий</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E99" t="str">
+        <f t="shared" si="3"/>
+        <v>mauritius</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="19.2">
+      <c r="A100" s="3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C100" t="str">
+        <f t="shared" si="2"/>
+        <v>мавритания</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E100" t="str">
+        <f t="shared" si="3"/>
+        <v>mauritania</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="19.2">
+      <c r="A101" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C101" t="str">
+        <f t="shared" si="2"/>
+        <v>мадагаскар</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E101" t="str">
+        <f t="shared" si="3"/>
+        <v>madagascar</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="19.2">
+      <c r="A102" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C102" t="str">
+        <f t="shared" si="2"/>
+        <v>северная македония</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E102" t="str">
+        <f t="shared" si="3"/>
+        <v>north macedonia</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="19.2">
+      <c r="A103" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C103" t="str">
+        <f t="shared" si="2"/>
+        <v>малави</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="E103" t="str">
+        <f t="shared" si="3"/>
+        <v>malawi</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="19.2">
+      <c r="A104" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C104" t="str">
+        <f t="shared" si="2"/>
+        <v>малайзия</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E104" t="str">
+        <f t="shared" si="3"/>
+        <v>malaysia</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="19.2">
+      <c r="A105" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C105" t="str">
+        <f t="shared" si="2"/>
+        <v>мали</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E105" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> mali </v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="19.2">
+      <c r="A106" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C106" t="str">
+        <f t="shared" si="2"/>
+        <v>мальдивы</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E106" t="str">
+        <f t="shared" si="3"/>
+        <v>maldives</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="19.2">
+      <c r="A107" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C107" t="str">
+        <f t="shared" si="2"/>
+        <v>мальта</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>1462</v>
+      </c>
+      <c r="E107" t="str">
+        <f t="shared" si="3"/>
+        <v>malta</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="19.2">
+      <c r="A108" s="3" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C108" t="str">
+        <f t="shared" si="2"/>
+        <v>мальтийский орден</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>1463</v>
+      </c>
+      <c r="E108" t="str">
+        <f t="shared" si="3"/>
+        <v>order of malta</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="19.2">
+      <c r="A109" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C109" t="str">
+        <f t="shared" si="2"/>
+        <v>марокко</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E109" t="str">
+        <f t="shared" si="3"/>
+        <v>morocco</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="19.2">
+      <c r="A110" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C110" t="str">
+        <f t="shared" si="2"/>
+        <v>маршалловы острова</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E110" t="str">
+        <f t="shared" si="3"/>
+        <v>marshall islands</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="19.2">
+      <c r="A111" s="3" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C111" t="str">
+        <f t="shared" si="2"/>
+        <v>мексика</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>1466</v>
+      </c>
+      <c r="E111" t="str">
+        <f t="shared" si="3"/>
+        <v>mexico</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="19.2">
+      <c r="A112" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C112" t="str">
+        <f t="shared" si="2"/>
+        <v>мозамбик</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>1467</v>
+      </c>
+      <c r="E112" t="str">
+        <f t="shared" si="3"/>
+        <v>mozambique</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="19.2">
+      <c r="A113" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C113" t="str">
+        <f t="shared" si="2"/>
+        <v>молдова</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>1468</v>
+      </c>
+      <c r="E113" t="str">
+        <f t="shared" si="3"/>
+        <v>moldova</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="19.2">
+      <c r="A114" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C114" t="str">
+        <f t="shared" si="2"/>
+        <v>монако</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E114" t="str">
+        <f t="shared" si="3"/>
+        <v>principality of monaco</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="19.2">
+      <c r="A115" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C115" t="str">
+        <f t="shared" si="2"/>
+        <v>монголия</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E115" t="str">
+        <f t="shared" si="3"/>
+        <v>mongolia</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="19.2">
+      <c r="A116" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C116" t="str">
+        <f t="shared" si="2"/>
+        <v>мьянма</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E116" t="str">
+        <f t="shared" si="3"/>
+        <v>myanmar</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="19.2">
+      <c r="A117" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C117" t="str">
+        <f t="shared" si="2"/>
+        <v>намибия</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E117" t="str">
+        <f t="shared" si="3"/>
+        <v>namibia</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="19.2">
+      <c r="A118" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C118" t="str">
+        <f t="shared" si="2"/>
+        <v>науру</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="E118" t="str">
+        <f t="shared" si="3"/>
+        <v>nauru</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="19.2">
+      <c r="A119" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C119" t="str">
+        <f t="shared" si="2"/>
+        <v>непал</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E119" t="str">
+        <f t="shared" si="3"/>
+        <v>nepal</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="19.2">
+      <c r="A120" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C120" t="str">
+        <f t="shared" si="2"/>
+        <v>нигер</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E120" t="str">
+        <f t="shared" si="3"/>
+        <v>niger</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="19.2">
+      <c r="A121" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C121" t="str">
+        <f t="shared" si="2"/>
+        <v>нигерия</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E121" t="str">
+        <f t="shared" si="3"/>
+        <v>nigeria</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="19.2">
+      <c r="A122" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C122" t="str">
+        <f t="shared" si="2"/>
+        <v>нидерланды</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>1477</v>
+      </c>
+      <c r="E122" t="str">
+        <f t="shared" si="3"/>
+        <v>netherlands</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="19.2">
+      <c r="A123" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C123" t="str">
+        <f t="shared" si="2"/>
+        <v>никарагуа</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E123" t="str">
+        <f t="shared" si="3"/>
+        <v>nicaragua</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="19.2">
+      <c r="A124" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C124" t="str">
+        <f t="shared" si="2"/>
+        <v>новая зеландия</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E124" t="str">
+        <f t="shared" si="3"/>
+        <v>new zealand</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="19.2">
+      <c r="A125" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C125" t="str">
+        <f t="shared" si="2"/>
+        <v>норвегия</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E125" t="str">
+        <f t="shared" si="3"/>
+        <v>norway</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="19.2">
+      <c r="A126" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C126" t="str">
+        <f t="shared" si="2"/>
+        <v>оаэ</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>1552</v>
+      </c>
+      <c r="E126" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> uae </v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="19.2">
+      <c r="A127" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C127" t="str">
+        <f t="shared" si="2"/>
+        <v>оман</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E127" t="str">
+        <f t="shared" si="3"/>
+        <v>oman</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="19.2">
+      <c r="A128" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B128" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C128" t="str">
+        <f t="shared" si="2"/>
+        <v>пакистан</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E128" t="str">
+        <f t="shared" si="3"/>
+        <v>pakistan</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="19.2">
+      <c r="A129" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C129" t="str">
+        <f t="shared" si="2"/>
+        <v>палау</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E129" t="str">
+        <f t="shared" si="3"/>
+        <v>palau</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="19.2">
+      <c r="A130" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C130" t="str">
+        <f t="shared" ref="C130:C193" si="4">LOWER(A130)</f>
+        <v>палестина</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E130" t="str">
+        <f t="shared" ref="E130:E193" si="5">LOWER(D130)</f>
+        <v>palestine</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="19.2">
+      <c r="A131" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B131" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C131" t="str">
+        <f t="shared" si="4"/>
+        <v>панама</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E131" t="str">
+        <f t="shared" si="5"/>
+        <v>panama</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="19.2">
+      <c r="A132" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C132" t="str">
+        <f>LOWER(A132)</f>
+        <v>папуа—новая гвинея</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E132" t="str">
+        <f t="shared" si="5"/>
+        <v>papua new guinea</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="19.2">
+      <c r="A133" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C133" t="str">
+        <f t="shared" si="4"/>
+        <v>парагвай</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E133" t="str">
+        <f t="shared" si="5"/>
+        <v>paraguay</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="19.2">
+      <c r="A134" s="3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C134" t="str">
+        <f t="shared" si="4"/>
+        <v>перу</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>1551</v>
+      </c>
+      <c r="E134" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> peru </v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="19.2">
+      <c r="A135" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C135" t="str">
+        <f t="shared" si="4"/>
+        <v>польша</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E135" t="str">
+        <f t="shared" si="5"/>
+        <v>poland</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="19.2">
+      <c r="A136" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C136" t="str">
+        <f t="shared" si="4"/>
+        <v>португалия</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E136" t="str">
+        <f t="shared" si="5"/>
+        <v>portugal</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="19.2">
+      <c r="A137" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C137" t="str">
+        <f t="shared" si="4"/>
+        <v>руанда</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E137" t="str">
+        <f t="shared" si="5"/>
+        <v>rwanda</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="19.2">
+      <c r="A138" s="3" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C138" t="str">
+        <f t="shared" si="4"/>
+        <v>румыния</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E138" t="str">
+        <f t="shared" si="5"/>
+        <v>romania</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="19.2">
+      <c r="A139" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C139" t="str">
+        <f t="shared" si="4"/>
+        <v>сальвадор</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E139" t="str">
+        <f t="shared" si="5"/>
+        <v>el salvador</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="19.2">
+      <c r="A140" s="3" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C140" t="str">
+        <f t="shared" si="4"/>
+        <v>самоа</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E140" t="str">
+        <f t="shared" si="5"/>
+        <v>samoa</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="19.2">
+      <c r="A141" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C141" t="str">
+        <f t="shared" si="4"/>
+        <v>сан-марино</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E141" t="str">
+        <f t="shared" si="5"/>
+        <v>san marino</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="19.2">
+      <c r="A142" s="3" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C142" t="str">
+        <f t="shared" si="4"/>
+        <v>сан-томеи принсипи</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E142" t="str">
+        <f t="shared" si="5"/>
+        <v>são tomé príncipe</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="19.2">
+      <c r="A143" s="3" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C143" t="str">
+        <f t="shared" si="4"/>
+        <v>саудовская аравия</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>1497</v>
+      </c>
+      <c r="E143" t="str">
+        <f t="shared" si="5"/>
+        <v>saudi arabia</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="19.2">
+      <c r="A144" s="3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C144" t="str">
+        <f t="shared" si="4"/>
+        <v>сейшельские острова</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E144" t="str">
+        <f t="shared" si="5"/>
+        <v>seychelles</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="19.2">
+      <c r="A145" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C145" t="str">
+        <f t="shared" si="4"/>
+        <v>сенегал</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>1499</v>
+      </c>
+      <c r="E145" t="str">
+        <f t="shared" si="5"/>
+        <v>senegal</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="38.4">
+      <c r="A146" s="3" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C146" t="str">
+        <f t="shared" si="4"/>
+        <v>сент-винсенти гренадины</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E146" t="str">
+        <f t="shared" si="5"/>
+        <v>saint vincent of the grenadines</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="19.2">
+      <c r="A147" s="3" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C147" t="str">
+        <f t="shared" si="4"/>
+        <v>сент-китси невис</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E147" t="str">
+        <f t="shared" si="5"/>
+        <v>saint kittsey nevis</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="19.2">
+      <c r="A148" s="3" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B148" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C148" t="str">
+        <f t="shared" si="4"/>
+        <v>сент-люсия</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E148" t="str">
+        <f t="shared" si="5"/>
+        <v>saint lucia</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="19.2">
+      <c r="A149" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B149" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C149" t="str">
+        <f t="shared" si="4"/>
+        <v>сербия</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E149" t="str">
+        <f t="shared" si="5"/>
+        <v>serbia</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="19.2">
+      <c r="A150" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B150" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C150" t="str">
+        <f t="shared" si="4"/>
+        <v>сингапур</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>1504</v>
+      </c>
+      <c r="E150" t="str">
+        <f t="shared" si="5"/>
+        <v>singapore</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="19.2">
+      <c r="A151" s="3" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B151" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C151" t="str">
+        <f t="shared" si="4"/>
+        <v>сирия</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E151" t="str">
+        <f t="shared" si="5"/>
+        <v>syria</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="19.2">
+      <c r="A152" s="3" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B152" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C152" t="str">
+        <f t="shared" si="4"/>
+        <v>словакия</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>1506</v>
+      </c>
+      <c r="E152" t="str">
+        <f t="shared" si="5"/>
+        <v>slovakia</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="19.2">
+      <c r="A153" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C153" t="str">
+        <f t="shared" si="4"/>
+        <v>словения</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E153" t="str">
+        <f t="shared" si="5"/>
+        <v>slovenia</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="19.2">
+      <c r="A154" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B154" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C154" t="str">
+        <f t="shared" si="4"/>
+        <v>соломоновы острова</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E154" t="str">
+        <f t="shared" si="5"/>
+        <v>solomon islands</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="19.2">
+      <c r="A155" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C155" t="str">
+        <f t="shared" si="4"/>
+        <v>сомали</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E155" t="str">
+        <f t="shared" si="5"/>
+        <v>somalia</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="19.2">
+      <c r="A156" s="3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C156" t="str">
+        <f t="shared" si="4"/>
+        <v>судан</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>1510</v>
+      </c>
+      <c r="E156" t="str">
+        <f t="shared" si="5"/>
+        <v>sudan</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="19.2">
+      <c r="A157" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B157" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C157" t="str">
+        <f t="shared" si="4"/>
+        <v>суринам</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E157" t="str">
+        <f t="shared" si="5"/>
+        <v>suriname</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="19.2">
+      <c r="A158" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B158" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C158" t="str">
+        <f t="shared" si="4"/>
+        <v>сша</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E158" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> usa </v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="19.2">
+      <c r="A159" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B159" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C159" t="str">
+        <f t="shared" si="4"/>
+        <v>сьерра-леоне</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>1512</v>
+      </c>
+      <c r="E159" t="str">
+        <f t="shared" si="5"/>
+        <v>sierra leone</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="19.2">
+      <c r="A160" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B160" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C160" t="str">
+        <f t="shared" si="4"/>
+        <v>таджикистан</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E160" t="str">
+        <f t="shared" si="5"/>
+        <v>таджикистан</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="19.2">
+      <c r="A161" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B161" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C161" t="str">
+        <f t="shared" si="4"/>
+        <v>таиланд</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E161" t="str">
+        <f t="shared" si="5"/>
+        <v>thailand</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="19.2">
+      <c r="A162" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B162" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C162" t="str">
+        <f t="shared" si="4"/>
+        <v>танзания</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>1514</v>
+      </c>
+      <c r="E162" t="str">
+        <f t="shared" si="5"/>
+        <v>tanzania</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="19.2">
+      <c r="A163" s="3" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B163" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C163" t="str">
+        <f t="shared" si="4"/>
+        <v>того</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>1515</v>
+      </c>
+      <c r="E163" t="str">
+        <f t="shared" si="5"/>
+        <v>togo</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="19.2">
+      <c r="A164" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B164" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C164" t="str">
+        <f t="shared" si="4"/>
+        <v>тонга</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>1516</v>
+      </c>
+      <c r="E164" t="str">
+        <f t="shared" si="5"/>
+        <v>tonga</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="19.2">
+      <c r="A165" s="3" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B165" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C165" t="str">
+        <f t="shared" si="4"/>
+        <v>тринидад и тобаго</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>1517</v>
+      </c>
+      <c r="E165" t="str">
+        <f t="shared" si="5"/>
+        <v>trinidad and tobago</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="19.2">
+      <c r="A166" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B166" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C166" t="str">
+        <f t="shared" si="4"/>
+        <v>тувалу</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E166" t="str">
+        <f t="shared" si="5"/>
+        <v>tuvalu</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="19.2">
+      <c r="A167" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B167" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C167" t="str">
+        <f t="shared" si="4"/>
+        <v>тунис</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>1519</v>
+      </c>
+      <c r="E167" t="str">
+        <f t="shared" si="5"/>
+        <v>tunisia</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="19.2">
+      <c r="A168" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B168" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C168" t="str">
+        <f t="shared" si="4"/>
+        <v>туркменистан</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>1520</v>
+      </c>
+      <c r="E168" t="str">
+        <f t="shared" si="5"/>
+        <v>turkmenistan</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="19.2">
+      <c r="A169" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B169" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C169" t="str">
+        <f t="shared" si="4"/>
+        <v>турция</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="E169" t="str">
+        <f t="shared" si="5"/>
+        <v>turkey</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="19.2">
+      <c r="A170" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B170" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C170" t="str">
+        <f t="shared" si="4"/>
+        <v>уганда</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E170" t="str">
+        <f t="shared" si="5"/>
+        <v>uganda</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="19.2">
+      <c r="A171" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B171" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C171" t="str">
+        <f t="shared" si="4"/>
+        <v>узбекистан</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E171" t="str">
+        <f t="shared" si="5"/>
+        <v>uzbekistan</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="19.2">
+      <c r="A172" s="3" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B172" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C172" t="str">
+        <f t="shared" si="4"/>
+        <v>украина</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>1524</v>
+      </c>
+      <c r="E172" t="str">
+        <f t="shared" si="5"/>
+        <v>ukraine</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="19.2">
+      <c r="A173" s="3" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B173" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C173" t="str">
+        <f t="shared" si="4"/>
+        <v>уругвай</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>1525</v>
+      </c>
+      <c r="E173" t="str">
+        <f t="shared" si="5"/>
+        <v>uruguay</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="38.4">
+      <c r="A174" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C174" t="str">
+        <f t="shared" si="4"/>
+        <v>федеративные штаты микронезии</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>1526</v>
+      </c>
+      <c r="E174" t="str">
+        <f t="shared" si="5"/>
+        <v>federated states of micronesia</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="19.2">
+      <c r="A175" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B175" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C175" t="str">
+        <f t="shared" si="4"/>
+        <v>фиджи</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>1550</v>
+      </c>
+      <c r="E175" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> fiji </v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="19.2">
+      <c r="A176" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C176" t="str">
+        <f t="shared" si="4"/>
+        <v>филиппины</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>1527</v>
+      </c>
+      <c r="E176" t="str">
+        <f t="shared" si="5"/>
+        <v>philippines</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="19.2">
+      <c r="A177" s="3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C177" t="str">
+        <f t="shared" si="4"/>
+        <v>финляндия</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>1528</v>
+      </c>
+      <c r="E177" t="str">
+        <f t="shared" si="5"/>
+        <v>finland</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="19.2">
+      <c r="A178" s="3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B178" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C178" t="str">
+        <f t="shared" si="4"/>
+        <v>франция</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>1529</v>
+      </c>
+      <c r="E178" t="str">
+        <f t="shared" si="5"/>
+        <v>france</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="19.2">
+      <c r="A179" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B179" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C179" t="str">
+        <f t="shared" si="4"/>
+        <v>хорватия</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E179" t="str">
+        <f t="shared" si="5"/>
+        <v>croatia</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="19.2">
+      <c r="A180" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B180" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C180" t="str">
+        <f t="shared" si="4"/>
+        <v>цар</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>1549</v>
+      </c>
+      <c r="E180" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> car </v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="19.2">
+      <c r="A181" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B181" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C181" t="str">
+        <f t="shared" si="4"/>
+        <v>чад</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>1531</v>
+      </c>
+      <c r="E181" t="str">
+        <f t="shared" si="5"/>
+        <v>chad</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="19.2">
+      <c r="A182" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B182" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C182" t="str">
+        <f t="shared" si="4"/>
+        <v>черногория</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>1532</v>
+      </c>
+      <c r="E182" t="str">
+        <f t="shared" si="5"/>
+        <v>montenegro</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="19.2">
+      <c r="A183" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B183" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C183" t="str">
+        <f t="shared" si="4"/>
+        <v>чехия</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>1533</v>
+      </c>
+      <c r="E183" t="str">
+        <f t="shared" si="5"/>
+        <v>czech republic</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="19.2">
+      <c r="A184" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B184" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C184" t="str">
+        <f t="shared" si="4"/>
+        <v>чили</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E184" t="str">
+        <f t="shared" si="5"/>
+        <v>chile</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="19.2">
+      <c r="A185" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B185" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C185" t="str">
+        <f t="shared" si="4"/>
+        <v>швейцария</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="E185" t="str">
+        <f t="shared" si="5"/>
+        <v>switzerland</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="19.2">
+      <c r="A186" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B186" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C186" t="str">
+        <f t="shared" si="4"/>
+        <v>швеция</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>1536</v>
+      </c>
+      <c r="E186" t="str">
+        <f t="shared" si="5"/>
+        <v>sweden</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="19.2">
+      <c r="A187" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B187" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C187" t="str">
+        <f t="shared" si="4"/>
+        <v>шри-ланка</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>1537</v>
+      </c>
+      <c r="E187" t="str">
+        <f t="shared" si="5"/>
+        <v>sri lanka</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="19.2">
+      <c r="A188" s="3" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B188" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C188" t="str">
+        <f t="shared" si="4"/>
+        <v>эквадор</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>1538</v>
+      </c>
+      <c r="E188" t="str">
+        <f t="shared" si="5"/>
+        <v>ecuador</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="19.2">
+      <c r="A189" s="3" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B189" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C189" t="str">
+        <f t="shared" si="4"/>
+        <v>экваториальная гвинея</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>1539</v>
+      </c>
+      <c r="E189" t="str">
+        <f t="shared" si="5"/>
+        <v>equatorial guinea</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="19.2">
+      <c r="A190" s="3" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B190" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C190" t="str">
+        <f t="shared" si="4"/>
+        <v>эритрея</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E190" t="str">
+        <f t="shared" si="5"/>
+        <v>eritrea</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="19.2">
+      <c r="A191" s="3" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B191" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C191" t="str">
+        <f t="shared" si="4"/>
+        <v>эсватини</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>1541</v>
+      </c>
+      <c r="E191" t="str">
+        <f t="shared" si="5"/>
+        <v>eswatini</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="19.2">
+      <c r="A192" s="3" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C192" t="str">
+        <f t="shared" si="4"/>
+        <v>эстония</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>1542</v>
+      </c>
+      <c r="E192" t="str">
+        <f t="shared" si="5"/>
+        <v>estonia</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="19.2">
+      <c r="A193" s="3" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B193" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C193" t="str">
+        <f t="shared" si="4"/>
+        <v>эфиопия</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>1543</v>
+      </c>
+      <c r="E193" t="str">
+        <f t="shared" si="5"/>
+        <v>ethiopia</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="19.2">
+      <c r="A194" s="3" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B194" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C194" t="str">
+        <f t="shared" ref="C194:C198" si="6">LOWER(A194)</f>
+        <v>юар</v>
+      </c>
+      <c r="D194" s="5" t="s">
+        <v>1544</v>
+      </c>
+      <c r="E194" t="str">
+        <f t="shared" ref="E194:E198" si="7">LOWER(D194)</f>
+        <v>south africa</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="19.2">
+      <c r="A195" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B195" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C195" t="str">
+        <f t="shared" si="6"/>
+        <v>южная осетия</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E195" t="str">
+        <f t="shared" si="7"/>
+        <v>south ossetia</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" ht="19.2">
+      <c r="A196" s="3" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B196" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C196" t="str">
+        <f t="shared" si="6"/>
+        <v>южный судан</v>
+      </c>
+      <c r="D196" s="5" t="s">
+        <v>1546</v>
+      </c>
+      <c r="E196" t="str">
+        <f t="shared" si="7"/>
+        <v>south sudan</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="19.2">
+      <c r="A197" s="3" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C197" t="str">
+        <f t="shared" si="6"/>
+        <v>ямайка</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="E197" t="str">
+        <f t="shared" si="7"/>
+        <v>jamaica</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="19.2">
+      <c r="A198" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C198" t="str">
+        <f t="shared" si="6"/>
+        <v>япония</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E198" t="str">
+        <f t="shared" si="7"/>
+        <v>japan</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>